--- a/tests/ProcessCore.Tests/TestObjects/fct_gcqtof_assay.xlsx
+++ b/tests/ProcessCore.Tests/TestObjects/fct_gcqtof_assay.xlsx
@@ -1,20 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F99EDA-FA90-42A1-BAD9-08813BA15E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="isa_assay" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="metabolite_extraction" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="gas_chromatography" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="mass_spec" state="visible" r:id="rId7"/>
+    <sheet name="isa_assay" sheetId="1" r:id="rId1"/>
+    <sheet name="metabolite_extraction" sheetId="2" r:id="rId2"/>
+    <sheet name="gas_chromatography" sheetId="3" r:id="rId3"/>
+    <sheet name="mass_spec" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1733" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="265">
   <si>
     <t>ASSAY</t>
   </si>
@@ -311,9 +315,6 @@
   </si>
   <si>
     <t>metabolites</t>
-  </si>
-  <si>
-    <t>user-specific</t>
   </si>
   <si>
     <t/>
@@ -818,14 +819,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -852,7 +853,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -868,8 +869,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="annotationTable0" displayName="annotationTable0" ref="A1:AL7" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A1:AL7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="annotationTable0" displayName="annotationTable0" ref="A1:AL7">
+  <autoFilter ref="A1:AL7" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -910,52 +911,52 @@
     <filterColumn colId="37" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="38">
-    <tableColumn id="1" name="Input [Sample Name]" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="Protocol Type" totalsRowFunction="none"/>
-    <tableColumn id="3" name="Term Source REF (DPBO:1000161)" totalsRowFunction="none"/>
-    <tableColumn id="4" name="Term Accession Number (DPBO:1000161)" totalsRowFunction="none"/>
-    <tableColumn id="5" name="Protocol REF" totalsRowFunction="none"/>
-    <tableColumn id="6" name="Parameter [Bio entity]" totalsRowFunction="none"/>
-    <tableColumn id="7" name="Term Source REF (DPBO:0000012)" totalsRowFunction="none"/>
-    <tableColumn id="8" name="Term Accession Number (DPBO:0000012)" totalsRowFunction="none"/>
-    <tableColumn id="9" name="Parameter [Biosource amount]" totalsRowFunction="none"/>
-    <tableColumn id="10" name="Unit" totalsRowFunction="none"/>
-    <tableColumn id="11" name="Term Source REF (DPBO:0000013)" totalsRowFunction="none"/>
-    <tableColumn id="12" name="Term Accession Number (DPBO:0000013)" totalsRowFunction="none"/>
-    <tableColumn id="13" name="Parameter [Biosource material state]" totalsRowFunction="none"/>
-    <tableColumn id="14" name="Term Source REF (DPBO:0010009)" totalsRowFunction="none"/>
-    <tableColumn id="15" name="Term Accession Number (DPBO:0010009)" totalsRowFunction="none"/>
-    <tableColumn id="16" name="Parameter [Extraction buffer]" totalsRowFunction="none"/>
-    <tableColumn id="17" name="Term Source REF (DPBO:0000050)" totalsRowFunction="none"/>
-    <tableColumn id="18" name="Term Accession Number (DPBO:0000050)" totalsRowFunction="none"/>
-    <tableColumn id="19" name="Parameter [Extraction buffer volume]" totalsRowFunction="none"/>
-    <tableColumn id="20" name="Term Source REF (DPBO:0000051)" totalsRowFunction="none"/>
-    <tableColumn id="21" name="Term Accession Number (DPBO:0000051)" totalsRowFunction="none"/>
-    <tableColumn id="22" name="Parameter [Internal standard]" totalsRowFunction="none"/>
-    <tableColumn id="23" name="Term Source REF (DPBO:0010012)" totalsRowFunction="none"/>
-    <tableColumn id="24" name="Term Accession Number (DPBO:0010012)" totalsRowFunction="none"/>
-    <tableColumn id="25" name="Parameter [Sample volume]" totalsRowFunction="none"/>
-    <tableColumn id="26" name="Unit " totalsRowFunction="none"/>
-    <tableColumn id="27" name="Term Source REF (DPBO:0010013)" totalsRowFunction="none"/>
-    <tableColumn id="28" name="Term Accession Number (DPBO:0010013)" totalsRowFunction="none"/>
-    <tableColumn id="29" name="Parameter [MS sample post-extraction]" totalsRowFunction="none"/>
-    <tableColumn id="30" name="Term Source REF (DPBO:0000043)" totalsRowFunction="none"/>
-    <tableColumn id="31" name="Term Accession Number (DPBO:0000043)" totalsRowFunction="none"/>
-    <tableColumn id="32" name="Parameter [MS sample resuspension]" totalsRowFunction="none"/>
-    <tableColumn id="33" name="Term Source REF (DPBO:0000044)" totalsRowFunction="none"/>
-    <tableColumn id="34" name="Term Accession Number (DPBO:0000044)" totalsRowFunction="none"/>
-    <tableColumn id="35" name="Parameter [MS derivatization]" totalsRowFunction="none"/>
-    <tableColumn id="36" name="Term Source REF (DPBO:0000052)" totalsRowFunction="none"/>
-    <tableColumn id="37" name="Term Accession Number (DPBO:0000052)" totalsRowFunction="none"/>
-    <tableColumn id="38" name="Output [Sample Name]" totalsRowFunction="none"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Input [Sample Name]" totalsRowLabel="Total"/>
+    <tableColumn id="40" xr3:uid="{1F7BA1E0-1B82-4D7F-A429-F68B89017AC6}" name="Protocol REF"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Protocol Type"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Term Source REF (DPBO:1000161)"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Term Accession Number (DPBO:1000161)"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Parameter [Bio entity]"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Term Source REF (DPBO:0000012)"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Term Accession Number (DPBO:0000012)"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Parameter [Biosource amount]"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Unit"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Term Source REF (DPBO:0000013)"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Term Accession Number (DPBO:0000013)"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Parameter [Biosource material state]"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Term Source REF (DPBO:0010009)"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Term Accession Number (DPBO:0010009)"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Parameter [Extraction buffer]"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Term Source REF (DPBO:0000050)"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Term Accession Number (DPBO:0000050)"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Parameter [Extraction buffer volume]"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Term Source REF (DPBO:0000051)"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Term Accession Number (DPBO:0000051)"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Parameter [Internal standard]"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Term Source REF (DPBO:0010012)"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Term Accession Number (DPBO:0010012)"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Parameter [Sample volume]"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Unit "/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Term Source REF (DPBO:0010013)"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Term Accession Number (DPBO:0010013)"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="Parameter [MS sample post-extraction]"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Term Source REF (DPBO:0000043)"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="Term Accession Number (DPBO:0000043)"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="Parameter [MS sample resuspension]"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="Term Source REF (DPBO:0000044)"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="Term Accession Number (DPBO:0000044)"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="Parameter [MS derivatization]"/>
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="Term Source REF (DPBO:0000052)"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="Term Accession Number (DPBO:0000052)"/>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="Output [Sample Name]"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" name="annotationTable1" displayName="annotationTable1" ref="A1:AH21" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A1:AH21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="annotationTable1" displayName="annotationTable1" ref="A1:AH21">
+  <autoFilter ref="A1:AH21" xr:uid="{00000000-0009-0000-0100-000002000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -992,48 +993,48 @@
     <filterColumn colId="33" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="34">
-    <tableColumn id="1" name="Input [Sample Name]" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="Protocol REF" totalsRowFunction="none"/>
-    <tableColumn id="3" name="Protocol Type" totalsRowFunction="none"/>
-    <tableColumn id="4" name="Term Source REF (DPBO:1000161)" totalsRowFunction="none"/>
-    <tableColumn id="5" name="Term Accession Number (DPBO:1000161)" totalsRowFunction="none"/>
-    <tableColumn id="6" name="Parameter [MS sample type]" totalsRowFunction="none"/>
-    <tableColumn id="7" name="Term Source REF (DPBO:0000045)" totalsRowFunction="none"/>
-    <tableColumn id="8" name="Term Accession Number (DPBO:0000045)" totalsRowFunction="none"/>
-    <tableColumn id="9" name="Parameter [Chromatography instrument model]" totalsRowFunction="none"/>
-    <tableColumn id="10" name="Term Source REF (DPBO:0000046)" totalsRowFunction="none"/>
-    <tableColumn id="11" name="Term Accession Number (DPBO:0000046)" totalsRowFunction="none"/>
-    <tableColumn id="12" name="Parameter [Chromatography autosampler model]" totalsRowFunction="none"/>
-    <tableColumn id="13" name="Term Source REF (DPBO:0000047)" totalsRowFunction="none"/>
-    <tableColumn id="14" name="Term Accession Number (DPBO:0000047)" totalsRowFunction="none"/>
-    <tableColumn id="15" name="Parameter [Chromatography column type]" totalsRowFunction="none"/>
-    <tableColumn id="16" name="Term Source REF (DPBO:0000053)" totalsRowFunction="none"/>
-    <tableColumn id="17" name="Term Accession Number (DPBO:0000053)" totalsRowFunction="none"/>
-    <tableColumn id="18" name="Parameter [Chromatography column model]" totalsRowFunction="none"/>
-    <tableColumn id="19" name="Term Source REF (DPBO:0000048)" totalsRowFunction="none"/>
-    <tableColumn id="20" name="Term Accession Number (DPBO:0000048)" totalsRowFunction="none"/>
-    <tableColumn id="21" name="Parameter [mobile phase]" totalsRowFunction="none"/>
-    <tableColumn id="22" name="Term Source REF (CHMO:0000995)" totalsRowFunction="none"/>
-    <tableColumn id="23" name="Term Accession Number (CHMO:0000995)" totalsRowFunction="none"/>
-    <tableColumn id="24" name="Parameter [Chromatography injection volume]" totalsRowFunction="none"/>
-    <tableColumn id="25" name="Unit" totalsRowFunction="none"/>
-    <tableColumn id="26" name="Term Source REF (DPBO:0010014)" totalsRowFunction="none"/>
-    <tableColumn id="27" name="Term Accession Number (DPBO:0010014)" totalsRowFunction="none"/>
-    <tableColumn id="28" name="Parameter [Chromatography injection mode]" totalsRowFunction="none"/>
-    <tableColumn id="29" name="Term Source REF (DPBO:0010015)" totalsRowFunction="none"/>
-    <tableColumn id="30" name="Term Accession Number (DPBO:0010015)" totalsRowFunction="none"/>
-    <tableColumn id="31" name="Parameter [Chromatography gradient]" totalsRowFunction="none"/>
-    <tableColumn id="32" name="Term Source REF (DPBO:0000081)" totalsRowFunction="none"/>
-    <tableColumn id="33" name="Term Accession Number (DPBO:0000081)" totalsRowFunction="none"/>
-    <tableColumn id="34" name="Output [Sample Name]" totalsRowFunction="none"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Input [Sample Name]" totalsRowLabel="Total"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Protocol REF"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Protocol Type"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Term Source REF (DPBO:1000161)"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Term Accession Number (DPBO:1000161)"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Parameter [MS sample type]"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Term Source REF (DPBO:0000045)"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Term Accession Number (DPBO:0000045)"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Parameter [Chromatography instrument model]"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Term Source REF (DPBO:0000046)"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Term Accession Number (DPBO:0000046)"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Parameter [Chromatography autosampler model]"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Term Source REF (DPBO:0000047)"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Term Accession Number (DPBO:0000047)"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Parameter [Chromatography column type]"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Term Source REF (DPBO:0000053)"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Term Accession Number (DPBO:0000053)"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Parameter [Chromatography column model]"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Term Source REF (DPBO:0000048)"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Term Accession Number (DPBO:0000048)"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="Parameter [mobile phase]"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0100-000016000000}" name="Term Source REF (CHMO:0000995)"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0100-000017000000}" name="Term Accession Number (CHMO:0000995)"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0100-000018000000}" name="Parameter [Chromatography injection volume]"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0100-000019000000}" name="Unit"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0100-00001A000000}" name="Term Source REF (DPBO:0010014)"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0100-00001B000000}" name="Term Accession Number (DPBO:0010014)"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0100-00001C000000}" name="Parameter [Chromatography injection mode]"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0100-00001D000000}" name="Term Source REF (DPBO:0010015)"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0100-00001E000000}" name="Term Accession Number (DPBO:0010015)"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0100-00001F000000}" name="Parameter [Chromatography gradient]"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0100-000020000000}" name="Term Source REF (DPBO:0000081)"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0100-000021000000}" name="Term Accession Number (DPBO:0000081)"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0100-000022000000}" name="Output [Sample Name]"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" name="annotationTable2" displayName="annotationTable2" ref="A1:AG21" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A1:AG21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="annotationTable2" displayName="annotationTable2" ref="A1:AG21">
+  <autoFilter ref="A1:AG21" xr:uid="{00000000-0009-0000-0100-000003000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -1069,39 +1070,39 @@
     <filterColumn colId="32" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="33">
-    <tableColumn id="1" name="Input [Sample Name]" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="Protocol Type" totalsRowFunction="none"/>
-    <tableColumn id="3" name="Term Source REF (DPBO:1000161)" totalsRowFunction="none"/>
-    <tableColumn id="4" name="Term Accession Number (DPBO:1000161)" totalsRowFunction="none"/>
-    <tableColumn id="5" name="Protocol REF" totalsRowFunction="none"/>
-    <tableColumn id="6" name="Parameter [scan polarity]" totalsRowFunction="none"/>
-    <tableColumn id="7" name="Term Source REF (MS:1000465)" totalsRowFunction="none"/>
-    <tableColumn id="8" name="Term Accession Number (MS:1000465)" totalsRowFunction="none"/>
-    <tableColumn id="9" name="Parameter [scan window lower limit]" totalsRowFunction="none"/>
-    <tableColumn id="10" name="Term Source REF (MS:1000501)" totalsRowFunction="none"/>
-    <tableColumn id="11" name="Term Accession Number (MS:1000501)" totalsRowFunction="none"/>
-    <tableColumn id="12" name="Parameter [scan window upper limit]" totalsRowFunction="none"/>
-    <tableColumn id="13" name="Term Source REF (MS:1000500)" totalsRowFunction="none"/>
-    <tableColumn id="14" name="Term Accession Number (MS:1000500)" totalsRowFunction="none"/>
-    <tableColumn id="15" name="Parameter [scan rate]" totalsRowFunction="none"/>
-    <tableColumn id="16" name="Unit" totalsRowFunction="none"/>
-    <tableColumn id="17" name="Term Source REF (MS:1000015)" totalsRowFunction="none"/>
-    <tableColumn id="18" name="Term Accession Number (MS:1000015)" totalsRowFunction="none"/>
-    <tableColumn id="19" name="Parameter [instrument model]" totalsRowFunction="none"/>
-    <tableColumn id="20" name="Term Source REF (MS:1000031)" totalsRowFunction="none"/>
-    <tableColumn id="21" name="Term Accession Number (MS:1000031)" totalsRowFunction="none"/>
-    <tableColumn id="22" name="Parameter [ionization type]" totalsRowFunction="none"/>
-    <tableColumn id="23" name="Term Source REF (MS:1000008)" totalsRowFunction="none"/>
-    <tableColumn id="24" name="Term Accession Number (MS:1000008)" totalsRowFunction="none"/>
-    <tableColumn id="25" name="Parameter [mass analyzer type]" totalsRowFunction="none"/>
-    <tableColumn id="26" name="Term Source REF (MS:1000443)" totalsRowFunction="none"/>
-    <tableColumn id="27" name="Term Accession Number (MS:1000443)" totalsRowFunction="none"/>
-    <tableColumn id="28" name="Parameter [detector type]" totalsRowFunction="none"/>
-    <tableColumn id="29" name="Term Source REF (MS:1000026)" totalsRowFunction="none"/>
-    <tableColumn id="30" name="Term Accession Number (MS:1000026)" totalsRowFunction="none"/>
-    <tableColumn id="31" name="Output [Data]" totalsRowFunction="none"/>
-    <tableColumn id="32" name="Data Format" totalsRowFunction="none"/>
-    <tableColumn id="33" name="Data Selector Format" totalsRowFunction="none"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Input [Sample Name]" totalsRowLabel="Total"/>
+    <tableColumn id="34" xr3:uid="{5D4C6266-2D76-457A-9C4F-7F612F8B3572}" name="Protocol REF"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Protocol Type"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Term Source REF (DPBO:1000161)"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Term Accession Number (DPBO:1000161)"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Parameter [scan polarity]"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Term Source REF (MS:1000465)"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Term Accession Number (MS:1000465)"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Parameter [scan window lower limit]"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Term Source REF (MS:1000501)"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Term Accession Number (MS:1000501)"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="Parameter [scan window upper limit]"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="Term Source REF (MS:1000500)"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="Term Accession Number (MS:1000500)"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0200-00000F000000}" name="Parameter [scan rate]"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0200-000010000000}" name="Unit"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0200-000011000000}" name="Term Source REF (MS:1000015)"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0200-000012000000}" name="Term Accession Number (MS:1000015)"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0200-000013000000}" name="Parameter [instrument model]"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0200-000014000000}" name="Term Source REF (MS:1000031)"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0200-000015000000}" name="Term Accession Number (MS:1000031)"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0200-000016000000}" name="Parameter [ionization type]"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0200-000017000000}" name="Term Source REF (MS:1000008)"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0200-000018000000}" name="Term Accession Number (MS:1000008)"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0200-000019000000}" name="Parameter [mass analyzer type]"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0200-00001A000000}" name="Term Source REF (MS:1000443)"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0200-00001B000000}" name="Term Accession Number (MS:1000443)"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0200-00001C000000}" name="Parameter [detector type]"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0200-00001D000000}" name="Term Source REF (MS:1000026)"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0200-00001E000000}" name="Term Accession Number (MS:1000026)"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0200-00001F000000}" name="Output [Data]"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0200-000020000000}" name="Data Format"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0200-000021000000}" name="Data Selector Format"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1403,16 +1404,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1420,7 +1421,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1428,7 +1429,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1436,7 +1437,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1444,17 +1445,17 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1462,7 +1463,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1470,7 +1471,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1478,7 +1479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1486,7 +1487,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1494,7 +1495,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1539,7 +1540,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -1555,7 +1556,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -1563,7 +1564,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -1623,7 +1624,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>51</v>
       </c>
@@ -1641,30 +1642,30 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AL7"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>55</v>
       </c>
       <c r="B1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" t="s">
         <v>56</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>57</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>58</v>
-      </c>
-      <c r="E1" t="s">
-        <v>59</v>
       </c>
       <c r="F1" t="s">
         <v>60</v>
@@ -1771,700 +1772,592 @@
         <v>93</v>
       </c>
       <c r="B2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" t="s">
         <v>94</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>95</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>96</v>
-      </c>
-      <c r="E2" t="s">
-        <v>97</v>
       </c>
       <c r="F2" t="s">
         <v>98</v>
       </c>
-      <c r="G2" t="s">
-        <v>99</v>
-      </c>
       <c r="H2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I2" t="s">
         <v>100</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>101</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>102</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>103</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>104</v>
-      </c>
-      <c r="M2" t="s">
-        <v>105</v>
       </c>
       <c r="N2" t="s">
         <v>95</v>
       </c>
       <c r="O2" t="s">
+        <v>105</v>
+      </c>
+      <c r="P2" t="s">
         <v>106</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
+        <v>99</v>
+      </c>
+      <c r="S2" t="s">
         <v>107</v>
       </c>
-      <c r="Q2" t="s">
-        <v>99</v>
-      </c>
-      <c r="R2" t="s">
-        <v>100</v>
-      </c>
-      <c r="S2" t="s">
+      <c r="U2" t="s">
+        <v>99</v>
+      </c>
+      <c r="V2" t="s">
         <v>108</v>
       </c>
-      <c r="T2" t="s">
-        <v>99</v>
-      </c>
-      <c r="U2" t="s">
-        <v>100</v>
-      </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>109</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>110</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>111</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>112</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB2" t="s">
         <v>113</v>
       </c>
-      <c r="AA2" t="s">
-        <v>103</v>
-      </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>114</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AE2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF2" t="s">
         <v>115</v>
       </c>
-      <c r="AD2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AF2" t="s">
+      <c r="AH2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AI2" t="s">
         <v>116</v>
       </c>
-      <c r="AG2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AI2" t="s">
+      <c r="AK2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL2" t="s">
         <v>117</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" t="s">
         <v>94</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>95</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>96</v>
-      </c>
-      <c r="E3" t="s">
-        <v>97</v>
       </c>
       <c r="F3" t="s">
         <v>98</v>
       </c>
-      <c r="G3" t="s">
-        <v>99</v>
-      </c>
       <c r="H3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K3" t="s">
         <v>102</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>103</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>104</v>
-      </c>
-      <c r="M3" t="s">
-        <v>105</v>
       </c>
       <c r="N3" t="s">
         <v>95</v>
       </c>
       <c r="O3" t="s">
+        <v>105</v>
+      </c>
+      <c r="P3" t="s">
         <v>106</v>
       </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S3" t="s">
         <v>107</v>
       </c>
-      <c r="Q3" t="s">
-        <v>99</v>
-      </c>
-      <c r="R3" t="s">
-        <v>100</v>
-      </c>
-      <c r="S3" t="s">
+      <c r="U3" t="s">
+        <v>99</v>
+      </c>
+      <c r="V3" t="s">
         <v>108</v>
       </c>
-      <c r="T3" t="s">
-        <v>99</v>
-      </c>
-      <c r="U3" t="s">
-        <v>100</v>
-      </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>109</v>
       </c>
-      <c r="W3" t="s">
+      <c r="X3" t="s">
         <v>110</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Y3" t="s">
         <v>111</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Z3" t="s">
         <v>112</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AA3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB3" t="s">
         <v>113</v>
       </c>
-      <c r="AA3" t="s">
-        <v>103</v>
-      </c>
-      <c r="AB3" t="s">
+      <c r="AC3" t="s">
         <v>114</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AE3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF3" t="s">
         <v>115</v>
       </c>
-      <c r="AD3" t="s">
-        <v>99</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>99</v>
-      </c>
       <c r="AH3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AI3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL3" t="s">
         <v>121</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>99</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" t="s">
         <v>94</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>95</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>96</v>
-      </c>
-      <c r="E4" t="s">
-        <v>97</v>
       </c>
       <c r="F4" t="s">
         <v>98</v>
       </c>
-      <c r="G4" t="s">
-        <v>99</v>
-      </c>
       <c r="H4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J4" t="s">
+        <v>101</v>
+      </c>
+      <c r="K4" t="s">
         <v>102</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>103</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>104</v>
-      </c>
-      <c r="M4" t="s">
-        <v>105</v>
       </c>
       <c r="N4" t="s">
         <v>95</v>
       </c>
       <c r="O4" t="s">
+        <v>105</v>
+      </c>
+      <c r="P4" t="s">
         <v>106</v>
       </c>
-      <c r="P4" t="s">
+      <c r="R4" t="s">
+        <v>99</v>
+      </c>
+      <c r="S4" t="s">
         <v>107</v>
       </c>
-      <c r="Q4" t="s">
-        <v>99</v>
-      </c>
-      <c r="R4" t="s">
-        <v>100</v>
-      </c>
-      <c r="S4" t="s">
+      <c r="U4" t="s">
+        <v>99</v>
+      </c>
+      <c r="V4" t="s">
         <v>108</v>
       </c>
-      <c r="T4" t="s">
-        <v>99</v>
-      </c>
-      <c r="U4" t="s">
-        <v>100</v>
-      </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>109</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>110</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>111</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>112</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB4" t="s">
         <v>113</v>
       </c>
-      <c r="AA4" t="s">
-        <v>103</v>
-      </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>114</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AE4" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF4" t="s">
         <v>115</v>
       </c>
-      <c r="AD4" t="s">
-        <v>99</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>100</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>116</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>99</v>
-      </c>
       <c r="AH4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AI4" t="s">
+        <v>124</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL4" t="s">
         <v>125</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>99</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>100</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" t="s">
         <v>94</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>95</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>96</v>
-      </c>
-      <c r="E5" t="s">
-        <v>97</v>
       </c>
       <c r="F5" t="s">
         <v>98</v>
       </c>
-      <c r="G5" t="s">
-        <v>99</v>
-      </c>
       <c r="H5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J5" t="s">
+        <v>101</v>
+      </c>
+      <c r="K5" t="s">
         <v>102</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>103</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>104</v>
-      </c>
-      <c r="M5" t="s">
-        <v>105</v>
       </c>
       <c r="N5" t="s">
         <v>95</v>
       </c>
       <c r="O5" t="s">
+        <v>105</v>
+      </c>
+      <c r="P5" t="s">
         <v>106</v>
       </c>
-      <c r="P5" t="s">
+      <c r="R5" t="s">
+        <v>99</v>
+      </c>
+      <c r="S5" t="s">
         <v>107</v>
       </c>
-      <c r="Q5" t="s">
-        <v>99</v>
-      </c>
-      <c r="R5" t="s">
-        <v>100</v>
-      </c>
-      <c r="S5" t="s">
+      <c r="U5" t="s">
+        <v>99</v>
+      </c>
+      <c r="V5" t="s">
         <v>108</v>
       </c>
-      <c r="T5" t="s">
-        <v>99</v>
-      </c>
-      <c r="U5" t="s">
-        <v>100</v>
-      </c>
-      <c r="V5" t="s">
+      <c r="W5" t="s">
         <v>109</v>
       </c>
-      <c r="W5" t="s">
+      <c r="X5" t="s">
         <v>110</v>
       </c>
-      <c r="X5" t="s">
+      <c r="Y5" t="s">
         <v>111</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="Z5" t="s">
         <v>112</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="AA5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB5" t="s">
         <v>113</v>
       </c>
-      <c r="AA5" t="s">
-        <v>103</v>
-      </c>
-      <c r="AB5" t="s">
+      <c r="AC5" t="s">
         <v>114</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AE5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF5" t="s">
         <v>115</v>
       </c>
-      <c r="AD5" t="s">
-        <v>99</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>100</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>116</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>99</v>
-      </c>
       <c r="AH5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AI5" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL5" t="s">
         <v>129</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>99</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>100</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" t="s">
         <v>94</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>95</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>96</v>
-      </c>
-      <c r="E6" t="s">
-        <v>97</v>
       </c>
       <c r="F6" t="s">
         <v>98</v>
       </c>
-      <c r="G6" t="s">
-        <v>99</v>
-      </c>
       <c r="H6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J6" t="s">
+        <v>101</v>
+      </c>
+      <c r="K6" t="s">
         <v>102</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>103</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>104</v>
-      </c>
-      <c r="M6" t="s">
-        <v>105</v>
       </c>
       <c r="N6" t="s">
         <v>95</v>
       </c>
       <c r="O6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P6" t="s">
         <v>106</v>
       </c>
-      <c r="P6" t="s">
+      <c r="R6" t="s">
+        <v>99</v>
+      </c>
+      <c r="S6" t="s">
         <v>107</v>
       </c>
-      <c r="Q6" t="s">
-        <v>99</v>
-      </c>
-      <c r="R6" t="s">
-        <v>100</v>
-      </c>
-      <c r="S6" t="s">
+      <c r="U6" t="s">
+        <v>99</v>
+      </c>
+      <c r="V6" t="s">
         <v>108</v>
       </c>
-      <c r="T6" t="s">
-        <v>99</v>
-      </c>
-      <c r="U6" t="s">
-        <v>100</v>
-      </c>
-      <c r="V6" t="s">
+      <c r="W6" t="s">
         <v>109</v>
       </c>
-      <c r="W6" t="s">
+      <c r="X6" t="s">
         <v>110</v>
       </c>
-      <c r="X6" t="s">
+      <c r="Y6" t="s">
         <v>111</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="Z6" t="s">
         <v>112</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="AA6" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB6" t="s">
         <v>113</v>
       </c>
-      <c r="AA6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AB6" t="s">
+      <c r="AC6" t="s">
         <v>114</v>
       </c>
-      <c r="AC6" t="s">
+      <c r="AE6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF6" t="s">
         <v>115</v>
       </c>
-      <c r="AD6" t="s">
-        <v>99</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>100</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>116</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>99</v>
-      </c>
       <c r="AH6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AI6" t="s">
-        <v>129</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="AK6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AL6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" t="s">
         <v>94</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>95</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>96</v>
-      </c>
-      <c r="E7" t="s">
-        <v>97</v>
       </c>
       <c r="F7" t="s">
         <v>98</v>
       </c>
-      <c r="G7" t="s">
-        <v>99</v>
-      </c>
       <c r="H7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J7" t="s">
+        <v>101</v>
+      </c>
+      <c r="K7" t="s">
         <v>102</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>103</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>104</v>
-      </c>
-      <c r="M7" t="s">
-        <v>105</v>
       </c>
       <c r="N7" t="s">
         <v>95</v>
       </c>
       <c r="O7" t="s">
+        <v>105</v>
+      </c>
+      <c r="P7" t="s">
         <v>106</v>
       </c>
-      <c r="P7" t="s">
+      <c r="R7" t="s">
+        <v>99</v>
+      </c>
+      <c r="S7" t="s">
         <v>107</v>
       </c>
-      <c r="Q7" t="s">
-        <v>99</v>
-      </c>
-      <c r="R7" t="s">
-        <v>100</v>
-      </c>
-      <c r="S7" t="s">
+      <c r="U7" t="s">
+        <v>99</v>
+      </c>
+      <c r="V7" t="s">
         <v>108</v>
       </c>
-      <c r="T7" t="s">
-        <v>99</v>
-      </c>
-      <c r="U7" t="s">
-        <v>100</v>
-      </c>
-      <c r="V7" t="s">
+      <c r="W7" t="s">
         <v>109</v>
       </c>
-      <c r="W7" t="s">
+      <c r="X7" t="s">
         <v>110</v>
       </c>
-      <c r="X7" t="s">
+      <c r="Y7" t="s">
         <v>111</v>
       </c>
-      <c r="Y7" t="s">
+      <c r="Z7" t="s">
         <v>112</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="AA7" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB7" t="s">
         <v>113</v>
       </c>
-      <c r="AA7" t="s">
-        <v>103</v>
-      </c>
-      <c r="AB7" t="s">
+      <c r="AC7" t="s">
         <v>114</v>
       </c>
-      <c r="AC7" t="s">
+      <c r="AE7" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF7" t="s">
         <v>115</v>
       </c>
-      <c r="AD7" t="s">
-        <v>99</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>100</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>116</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>99</v>
-      </c>
       <c r="AH7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AI7" t="s">
-        <v>129</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="AK7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AL7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -2472,9 +2365,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AH21"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2493,88 +2386,88 @@
         <v>58</v>
       </c>
       <c r="F1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1" t="s">
         <v>137</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>138</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>139</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>140</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>141</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>142</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>143</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>144</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>145</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>146</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>147</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>148</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>149</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>150</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>151</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>152</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>153</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>154</v>
-      </c>
-      <c r="X1" t="s">
-        <v>155</v>
       </c>
       <c r="Y1" t="s">
         <v>64</v>
       </c>
       <c r="Z1" t="s">
+        <v>155</v>
+      </c>
+      <c r="AA1" t="s">
         <v>156</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>157</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>158</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>159</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>160</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>161</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>162</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>163</v>
       </c>
       <c r="AH1" t="s">
         <v>92</v>
@@ -2582,2087 +2475,1757 @@
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B2" t="s">
         <v>164</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>165</v>
-      </c>
-      <c r="C2" t="s">
-        <v>166</v>
       </c>
       <c r="D2" t="s">
         <v>95</v>
       </c>
       <c r="E2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I2" t="s">
         <v>167</v>
       </c>
-      <c r="F2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L2" t="s">
         <v>168</v>
       </c>
-      <c r="J2" t="s">
-        <v>99</v>
-      </c>
-      <c r="K2" t="s">
-        <v>100</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
+        <v>99</v>
+      </c>
+      <c r="O2" t="s">
         <v>169</v>
       </c>
-      <c r="M2" t="s">
-        <v>99</v>
-      </c>
-      <c r="N2" t="s">
-        <v>100</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
+        <v>99</v>
+      </c>
+      <c r="R2" t="s">
         <v>170</v>
       </c>
-      <c r="P2" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>100</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
+        <v>99</v>
+      </c>
+      <c r="U2" t="s">
         <v>171</v>
       </c>
-      <c r="S2" t="s">
-        <v>99</v>
-      </c>
-      <c r="T2" t="s">
-        <v>100</v>
-      </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
+        <v>109</v>
+      </c>
+      <c r="W2" t="s">
         <v>172</v>
       </c>
-      <c r="V2" t="s">
-        <v>110</v>
-      </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>173</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB2" t="s">
         <v>174</v>
       </c>
-      <c r="Y2" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>114</v>
-      </c>
-      <c r="AB2" t="s">
+      <c r="AD2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE2" t="s">
         <v>175</v>
       </c>
-      <c r="AC2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE2" t="s">
+      <c r="AG2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH2" t="s">
         <v>176</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B3" t="s">
         <v>164</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>165</v>
-      </c>
-      <c r="C3" t="s">
-        <v>166</v>
       </c>
       <c r="D3" t="s">
         <v>95</v>
       </c>
       <c r="E3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I3" t="s">
         <v>167</v>
       </c>
-      <c r="F3" t="s">
-        <v>100</v>
-      </c>
-      <c r="G3" t="s">
-        <v>100</v>
-      </c>
-      <c r="H3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L3" t="s">
         <v>168</v>
       </c>
-      <c r="J3" t="s">
-        <v>99</v>
-      </c>
-      <c r="K3" t="s">
-        <v>100</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="N3" t="s">
+        <v>99</v>
+      </c>
+      <c r="O3" t="s">
         <v>169</v>
       </c>
-      <c r="M3" t="s">
-        <v>99</v>
-      </c>
-      <c r="N3" t="s">
-        <v>100</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="Q3" t="s">
+        <v>99</v>
+      </c>
+      <c r="R3" t="s">
         <v>170</v>
       </c>
-      <c r="P3" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>100</v>
-      </c>
-      <c r="R3" t="s">
+      <c r="T3" t="s">
+        <v>99</v>
+      </c>
+      <c r="U3" t="s">
         <v>171</v>
       </c>
-      <c r="S3" t="s">
-        <v>99</v>
-      </c>
-      <c r="T3" t="s">
-        <v>100</v>
-      </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
+        <v>109</v>
+      </c>
+      <c r="W3" t="s">
         <v>172</v>
       </c>
-      <c r="V3" t="s">
-        <v>110</v>
-      </c>
-      <c r="W3" t="s">
+      <c r="X3" t="s">
         <v>173</v>
       </c>
-      <c r="X3" t="s">
-        <v>174</v>
-      </c>
       <c r="Y3" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA3" t="s">
         <v>113</v>
       </c>
-      <c r="Z3" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>114</v>
-      </c>
       <c r="AB3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC3" t="s">
         <v>178</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AD3" t="s">
         <v>179</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AE3" t="s">
+        <v>175</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH3" t="s">
         <v>180</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" t="s">
         <v>165</v>
-      </c>
-      <c r="C4" t="s">
-        <v>166</v>
       </c>
       <c r="D4" t="s">
         <v>95</v>
       </c>
       <c r="E4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I4" t="s">
         <v>167</v>
       </c>
-      <c r="F4" t="s">
-        <v>100</v>
-      </c>
-      <c r="G4" t="s">
-        <v>100</v>
-      </c>
-      <c r="H4" t="s">
-        <v>100</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
+        <v>99</v>
+      </c>
+      <c r="L4" t="s">
         <v>168</v>
       </c>
-      <c r="J4" t="s">
-        <v>99</v>
-      </c>
-      <c r="K4" t="s">
-        <v>100</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="N4" t="s">
+        <v>99</v>
+      </c>
+      <c r="O4" t="s">
         <v>169</v>
       </c>
-      <c r="M4" t="s">
-        <v>99</v>
-      </c>
-      <c r="N4" t="s">
-        <v>100</v>
-      </c>
-      <c r="O4" t="s">
+      <c r="Q4" t="s">
+        <v>99</v>
+      </c>
+      <c r="R4" t="s">
         <v>170</v>
       </c>
-      <c r="P4" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>100</v>
-      </c>
-      <c r="R4" t="s">
+      <c r="T4" t="s">
+        <v>99</v>
+      </c>
+      <c r="U4" t="s">
         <v>171</v>
       </c>
-      <c r="S4" t="s">
-        <v>99</v>
-      </c>
-      <c r="T4" t="s">
-        <v>100</v>
-      </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
+        <v>109</v>
+      </c>
+      <c r="W4" t="s">
         <v>172</v>
       </c>
-      <c r="V4" t="s">
-        <v>110</v>
-      </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>173</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB4" t="s">
         <v>174</v>
       </c>
-      <c r="Y4" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>114</v>
-      </c>
-      <c r="AB4" t="s">
+      <c r="AD4" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE4" t="s">
         <v>175</v>
       </c>
-      <c r="AC4" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>99</v>
-      </c>
       <c r="AG4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AH4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" t="s">
         <v>165</v>
-      </c>
-      <c r="C5" t="s">
-        <v>166</v>
       </c>
       <c r="D5" t="s">
         <v>95</v>
       </c>
       <c r="E5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F5" t="s">
+        <v>99</v>
+      </c>
+      <c r="G5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I5" t="s">
         <v>167</v>
       </c>
-      <c r="F5" t="s">
-        <v>100</v>
-      </c>
-      <c r="G5" t="s">
-        <v>100</v>
-      </c>
-      <c r="H5" t="s">
-        <v>100</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="K5" t="s">
+        <v>99</v>
+      </c>
+      <c r="L5" t="s">
         <v>168</v>
       </c>
-      <c r="J5" t="s">
-        <v>99</v>
-      </c>
-      <c r="K5" t="s">
-        <v>100</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="N5" t="s">
+        <v>99</v>
+      </c>
+      <c r="O5" t="s">
         <v>169</v>
       </c>
-      <c r="M5" t="s">
-        <v>99</v>
-      </c>
-      <c r="N5" t="s">
-        <v>100</v>
-      </c>
-      <c r="O5" t="s">
+      <c r="Q5" t="s">
+        <v>99</v>
+      </c>
+      <c r="R5" t="s">
         <v>170</v>
       </c>
-      <c r="P5" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>100</v>
-      </c>
-      <c r="R5" t="s">
+      <c r="T5" t="s">
+        <v>99</v>
+      </c>
+      <c r="U5" t="s">
         <v>171</v>
       </c>
-      <c r="S5" t="s">
-        <v>99</v>
-      </c>
-      <c r="T5" t="s">
-        <v>100</v>
-      </c>
-      <c r="U5" t="s">
+      <c r="V5" t="s">
+        <v>109</v>
+      </c>
+      <c r="W5" t="s">
         <v>172</v>
       </c>
-      <c r="V5" t="s">
-        <v>110</v>
-      </c>
-      <c r="W5" t="s">
+      <c r="X5" t="s">
         <v>173</v>
       </c>
-      <c r="X5" t="s">
-        <v>174</v>
-      </c>
       <c r="Y5" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA5" t="s">
         <v>113</v>
       </c>
-      <c r="Z5" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>114</v>
-      </c>
       <c r="AB5" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC5" t="s">
         <v>178</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AD5" t="s">
         <v>179</v>
       </c>
-      <c r="AD5" t="s">
-        <v>180</v>
-      </c>
       <c r="AE5" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AG5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AH5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" t="s">
         <v>165</v>
-      </c>
-      <c r="C6" t="s">
-        <v>166</v>
       </c>
       <c r="D6" t="s">
         <v>95</v>
       </c>
       <c r="E6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H6" t="s">
+        <v>186</v>
+      </c>
+      <c r="I6" t="s">
         <v>167</v>
       </c>
-      <c r="F6" t="s">
-        <v>185</v>
-      </c>
-      <c r="G6" t="s">
-        <v>186</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="K6" t="s">
+        <v>99</v>
+      </c>
+      <c r="L6" t="s">
+        <v>168</v>
+      </c>
+      <c r="N6" t="s">
+        <v>99</v>
+      </c>
+      <c r="O6" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>99</v>
+      </c>
+      <c r="R6" t="s">
+        <v>170</v>
+      </c>
+      <c r="T6" t="s">
+        <v>99</v>
+      </c>
+      <c r="U6" t="s">
+        <v>171</v>
+      </c>
+      <c r="V6" t="s">
+        <v>109</v>
+      </c>
+      <c r="W6" t="s">
+        <v>172</v>
+      </c>
+      <c r="X6" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>174</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>175</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH6" t="s">
         <v>187</v>
-      </c>
-      <c r="I6" t="s">
-        <v>168</v>
-      </c>
-      <c r="J6" t="s">
-        <v>99</v>
-      </c>
-      <c r="K6" t="s">
-        <v>100</v>
-      </c>
-      <c r="L6" t="s">
-        <v>169</v>
-      </c>
-      <c r="M6" t="s">
-        <v>99</v>
-      </c>
-      <c r="N6" t="s">
-        <v>100</v>
-      </c>
-      <c r="O6" t="s">
-        <v>170</v>
-      </c>
-      <c r="P6" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>100</v>
-      </c>
-      <c r="R6" t="s">
-        <v>171</v>
-      </c>
-      <c r="S6" t="s">
-        <v>99</v>
-      </c>
-      <c r="T6" t="s">
-        <v>100</v>
-      </c>
-      <c r="U6" t="s">
-        <v>172</v>
-      </c>
-      <c r="V6" t="s">
-        <v>110</v>
-      </c>
-      <c r="W6" t="s">
-        <v>173</v>
-      </c>
-      <c r="X6" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>114</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>175</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>100</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C7" t="s">
         <v>165</v>
-      </c>
-      <c r="C7" t="s">
-        <v>166</v>
       </c>
       <c r="D7" t="s">
         <v>95</v>
       </c>
       <c r="E7" t="s">
+        <v>166</v>
+      </c>
+      <c r="F7" t="s">
+        <v>184</v>
+      </c>
+      <c r="G7" t="s">
+        <v>185</v>
+      </c>
+      <c r="H7" t="s">
+        <v>186</v>
+      </c>
+      <c r="I7" t="s">
         <v>167</v>
       </c>
-      <c r="F7" t="s">
-        <v>185</v>
-      </c>
-      <c r="G7" t="s">
-        <v>186</v>
-      </c>
-      <c r="H7" t="s">
-        <v>187</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="K7" t="s">
+        <v>99</v>
+      </c>
+      <c r="L7" t="s">
         <v>168</v>
       </c>
-      <c r="J7" t="s">
-        <v>99</v>
-      </c>
-      <c r="K7" t="s">
-        <v>100</v>
-      </c>
-      <c r="L7" t="s">
+      <c r="N7" t="s">
+        <v>99</v>
+      </c>
+      <c r="O7" t="s">
         <v>169</v>
       </c>
-      <c r="M7" t="s">
-        <v>99</v>
-      </c>
-      <c r="N7" t="s">
-        <v>100</v>
-      </c>
-      <c r="O7" t="s">
+      <c r="Q7" t="s">
+        <v>99</v>
+      </c>
+      <c r="R7" t="s">
         <v>170</v>
       </c>
-      <c r="P7" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>100</v>
-      </c>
-      <c r="R7" t="s">
+      <c r="T7" t="s">
+        <v>99</v>
+      </c>
+      <c r="U7" t="s">
         <v>171</v>
       </c>
-      <c r="S7" t="s">
-        <v>99</v>
-      </c>
-      <c r="T7" t="s">
-        <v>100</v>
-      </c>
-      <c r="U7" t="s">
+      <c r="V7" t="s">
+        <v>109</v>
+      </c>
+      <c r="W7" t="s">
         <v>172</v>
       </c>
-      <c r="V7" t="s">
-        <v>110</v>
-      </c>
-      <c r="W7" t="s">
+      <c r="X7" t="s">
         <v>173</v>
       </c>
-      <c r="X7" t="s">
-        <v>174</v>
-      </c>
       <c r="Y7" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA7" t="s">
         <v>113</v>
       </c>
-      <c r="Z7" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>114</v>
-      </c>
       <c r="AB7" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC7" t="s">
         <v>178</v>
       </c>
-      <c r="AC7" t="s">
+      <c r="AD7" t="s">
         <v>179</v>
       </c>
-      <c r="AD7" t="s">
-        <v>180</v>
-      </c>
       <c r="AE7" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AG7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AH7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C8" t="s">
         <v>165</v>
-      </c>
-      <c r="C8" t="s">
-        <v>166</v>
       </c>
       <c r="D8" t="s">
         <v>95</v>
       </c>
       <c r="E8" t="s">
+        <v>166</v>
+      </c>
+      <c r="F8" t="s">
+        <v>184</v>
+      </c>
+      <c r="G8" t="s">
+        <v>185</v>
+      </c>
+      <c r="H8" t="s">
+        <v>186</v>
+      </c>
+      <c r="I8" t="s">
         <v>167</v>
       </c>
-      <c r="F8" t="s">
-        <v>185</v>
-      </c>
-      <c r="G8" t="s">
-        <v>186</v>
-      </c>
-      <c r="H8" t="s">
-        <v>187</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="K8" t="s">
+        <v>99</v>
+      </c>
+      <c r="L8" t="s">
         <v>168</v>
       </c>
-      <c r="J8" t="s">
-        <v>99</v>
-      </c>
-      <c r="K8" t="s">
-        <v>100</v>
-      </c>
-      <c r="L8" t="s">
+      <c r="N8" t="s">
+        <v>99</v>
+      </c>
+      <c r="O8" t="s">
         <v>169</v>
       </c>
-      <c r="M8" t="s">
-        <v>99</v>
-      </c>
-      <c r="N8" t="s">
-        <v>100</v>
-      </c>
-      <c r="O8" t="s">
+      <c r="Q8" t="s">
+        <v>99</v>
+      </c>
+      <c r="R8" t="s">
         <v>170</v>
       </c>
-      <c r="P8" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>100</v>
-      </c>
-      <c r="R8" t="s">
+      <c r="T8" t="s">
+        <v>99</v>
+      </c>
+      <c r="U8" t="s">
         <v>171</v>
       </c>
-      <c r="S8" t="s">
-        <v>99</v>
-      </c>
-      <c r="T8" t="s">
-        <v>100</v>
-      </c>
-      <c r="U8" t="s">
+      <c r="V8" t="s">
+        <v>109</v>
+      </c>
+      <c r="W8" t="s">
         <v>172</v>
       </c>
-      <c r="V8" t="s">
-        <v>110</v>
-      </c>
-      <c r="W8" t="s">
+      <c r="X8" t="s">
         <v>173</v>
       </c>
-      <c r="X8" t="s">
+      <c r="Y8" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB8" t="s">
         <v>174</v>
       </c>
-      <c r="Y8" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>114</v>
-      </c>
-      <c r="AB8" t="s">
+      <c r="AD8" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE8" t="s">
         <v>175</v>
       </c>
-      <c r="AC8" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>99</v>
-      </c>
       <c r="AG8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AH8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" t="s">
         <v>165</v>
-      </c>
-      <c r="C9" t="s">
-        <v>166</v>
       </c>
       <c r="D9" t="s">
         <v>95</v>
       </c>
       <c r="E9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F9" t="s">
+        <v>184</v>
+      </c>
+      <c r="G9" t="s">
+        <v>185</v>
+      </c>
+      <c r="H9" t="s">
+        <v>186</v>
+      </c>
+      <c r="I9" t="s">
         <v>167</v>
       </c>
-      <c r="F9" t="s">
-        <v>185</v>
-      </c>
-      <c r="G9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H9" t="s">
-        <v>187</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="K9" t="s">
+        <v>99</v>
+      </c>
+      <c r="L9" t="s">
         <v>168</v>
       </c>
-      <c r="J9" t="s">
-        <v>99</v>
-      </c>
-      <c r="K9" t="s">
-        <v>100</v>
-      </c>
-      <c r="L9" t="s">
+      <c r="N9" t="s">
+        <v>99</v>
+      </c>
+      <c r="O9" t="s">
         <v>169</v>
       </c>
-      <c r="M9" t="s">
-        <v>99</v>
-      </c>
-      <c r="N9" t="s">
-        <v>100</v>
-      </c>
-      <c r="O9" t="s">
+      <c r="Q9" t="s">
+        <v>99</v>
+      </c>
+      <c r="R9" t="s">
         <v>170</v>
       </c>
-      <c r="P9" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>100</v>
-      </c>
-      <c r="R9" t="s">
+      <c r="T9" t="s">
+        <v>99</v>
+      </c>
+      <c r="U9" t="s">
         <v>171</v>
       </c>
-      <c r="S9" t="s">
-        <v>99</v>
-      </c>
-      <c r="T9" t="s">
-        <v>100</v>
-      </c>
-      <c r="U9" t="s">
+      <c r="V9" t="s">
+        <v>109</v>
+      </c>
+      <c r="W9" t="s">
         <v>172</v>
       </c>
-      <c r="V9" t="s">
-        <v>110</v>
-      </c>
-      <c r="W9" t="s">
+      <c r="X9" t="s">
         <v>173</v>
       </c>
-      <c r="X9" t="s">
-        <v>174</v>
-      </c>
       <c r="Y9" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA9" t="s">
         <v>113</v>
       </c>
-      <c r="Z9" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>114</v>
-      </c>
       <c r="AB9" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC9" t="s">
         <v>178</v>
       </c>
-      <c r="AC9" t="s">
+      <c r="AD9" t="s">
         <v>179</v>
       </c>
-      <c r="AD9" t="s">
-        <v>180</v>
-      </c>
       <c r="AE9" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AG9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AH9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B10" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10" t="s">
         <v>165</v>
-      </c>
-      <c r="C10" t="s">
-        <v>166</v>
       </c>
       <c r="D10" t="s">
         <v>95</v>
       </c>
       <c r="E10" t="s">
+        <v>166</v>
+      </c>
+      <c r="F10" t="s">
+        <v>184</v>
+      </c>
+      <c r="G10" t="s">
+        <v>185</v>
+      </c>
+      <c r="H10" t="s">
+        <v>186</v>
+      </c>
+      <c r="I10" t="s">
         <v>167</v>
       </c>
-      <c r="F10" t="s">
-        <v>185</v>
-      </c>
-      <c r="G10" t="s">
-        <v>186</v>
-      </c>
-      <c r="H10" t="s">
-        <v>187</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="K10" t="s">
+        <v>99</v>
+      </c>
+      <c r="L10" t="s">
         <v>168</v>
       </c>
-      <c r="J10" t="s">
-        <v>99</v>
-      </c>
-      <c r="K10" t="s">
-        <v>100</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="N10" t="s">
+        <v>99</v>
+      </c>
+      <c r="O10" t="s">
         <v>169</v>
       </c>
-      <c r="M10" t="s">
-        <v>99</v>
-      </c>
-      <c r="N10" t="s">
-        <v>100</v>
-      </c>
-      <c r="O10" t="s">
+      <c r="Q10" t="s">
+        <v>99</v>
+      </c>
+      <c r="R10" t="s">
         <v>170</v>
       </c>
-      <c r="P10" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>100</v>
-      </c>
-      <c r="R10" t="s">
+      <c r="T10" t="s">
+        <v>99</v>
+      </c>
+      <c r="U10" t="s">
         <v>171</v>
       </c>
-      <c r="S10" t="s">
-        <v>99</v>
-      </c>
-      <c r="T10" t="s">
-        <v>100</v>
-      </c>
-      <c r="U10" t="s">
+      <c r="V10" t="s">
+        <v>109</v>
+      </c>
+      <c r="W10" t="s">
         <v>172</v>
       </c>
-      <c r="V10" t="s">
-        <v>110</v>
-      </c>
-      <c r="W10" t="s">
+      <c r="X10" t="s">
         <v>173</v>
       </c>
-      <c r="X10" t="s">
+      <c r="Y10" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB10" t="s">
         <v>174</v>
       </c>
-      <c r="Y10" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>114</v>
-      </c>
-      <c r="AB10" t="s">
+      <c r="AD10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE10" t="s">
         <v>175</v>
       </c>
-      <c r="AC10" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>99</v>
-      </c>
       <c r="AG10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AH10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B11" t="s">
+        <v>164</v>
+      </c>
+      <c r="C11" t="s">
         <v>165</v>
-      </c>
-      <c r="C11" t="s">
-        <v>166</v>
       </c>
       <c r="D11" t="s">
         <v>95</v>
       </c>
       <c r="E11" t="s">
+        <v>166</v>
+      </c>
+      <c r="F11" t="s">
+        <v>184</v>
+      </c>
+      <c r="G11" t="s">
+        <v>185</v>
+      </c>
+      <c r="H11" t="s">
+        <v>186</v>
+      </c>
+      <c r="I11" t="s">
         <v>167</v>
       </c>
-      <c r="F11" t="s">
-        <v>185</v>
-      </c>
-      <c r="G11" t="s">
-        <v>186</v>
-      </c>
-      <c r="H11" t="s">
-        <v>187</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="K11" t="s">
+        <v>99</v>
+      </c>
+      <c r="L11" t="s">
         <v>168</v>
       </c>
-      <c r="J11" t="s">
-        <v>99</v>
-      </c>
-      <c r="K11" t="s">
-        <v>100</v>
-      </c>
-      <c r="L11" t="s">
+      <c r="N11" t="s">
+        <v>99</v>
+      </c>
+      <c r="O11" t="s">
         <v>169</v>
       </c>
-      <c r="M11" t="s">
-        <v>99</v>
-      </c>
-      <c r="N11" t="s">
-        <v>100</v>
-      </c>
-      <c r="O11" t="s">
+      <c r="Q11" t="s">
+        <v>99</v>
+      </c>
+      <c r="R11" t="s">
         <v>170</v>
       </c>
-      <c r="P11" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>100</v>
-      </c>
-      <c r="R11" t="s">
+      <c r="T11" t="s">
+        <v>99</v>
+      </c>
+      <c r="U11" t="s">
         <v>171</v>
       </c>
-      <c r="S11" t="s">
-        <v>99</v>
-      </c>
-      <c r="T11" t="s">
-        <v>100</v>
-      </c>
-      <c r="U11" t="s">
+      <c r="V11" t="s">
+        <v>109</v>
+      </c>
+      <c r="W11" t="s">
         <v>172</v>
       </c>
-      <c r="V11" t="s">
-        <v>110</v>
-      </c>
-      <c r="W11" t="s">
+      <c r="X11" t="s">
         <v>173</v>
       </c>
-      <c r="X11" t="s">
-        <v>174</v>
-      </c>
       <c r="Y11" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA11" t="s">
         <v>113</v>
       </c>
-      <c r="Z11" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>114</v>
-      </c>
       <c r="AB11" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC11" t="s">
         <v>178</v>
       </c>
-      <c r="AC11" t="s">
+      <c r="AD11" t="s">
         <v>179</v>
       </c>
-      <c r="AD11" t="s">
-        <v>180</v>
-      </c>
       <c r="AE11" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AG11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AH11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>163</v>
+      </c>
+      <c r="B12" t="s">
         <v>164</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>165</v>
-      </c>
-      <c r="C12" t="s">
-        <v>166</v>
       </c>
       <c r="D12" t="s">
         <v>95</v>
       </c>
       <c r="E12" t="s">
+        <v>166</v>
+      </c>
+      <c r="F12" t="s">
+        <v>99</v>
+      </c>
+      <c r="G12" t="s">
+        <v>99</v>
+      </c>
+      <c r="H12" t="s">
+        <v>99</v>
+      </c>
+      <c r="I12" t="s">
         <v>167</v>
       </c>
-      <c r="F12" t="s">
-        <v>100</v>
-      </c>
-      <c r="G12" t="s">
-        <v>100</v>
-      </c>
-      <c r="H12" t="s">
-        <v>100</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="K12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L12" t="s">
         <v>168</v>
       </c>
-      <c r="J12" t="s">
-        <v>99</v>
-      </c>
-      <c r="K12" t="s">
-        <v>100</v>
-      </c>
-      <c r="L12" t="s">
+      <c r="N12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O12" t="s">
         <v>169</v>
       </c>
-      <c r="M12" t="s">
-        <v>99</v>
-      </c>
-      <c r="N12" t="s">
-        <v>100</v>
-      </c>
-      <c r="O12" t="s">
+      <c r="Q12" t="s">
+        <v>99</v>
+      </c>
+      <c r="R12" t="s">
         <v>170</v>
       </c>
-      <c r="P12" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>100</v>
-      </c>
-      <c r="R12" t="s">
+      <c r="T12" t="s">
+        <v>99</v>
+      </c>
+      <c r="U12" t="s">
         <v>171</v>
       </c>
-      <c r="S12" t="s">
-        <v>99</v>
-      </c>
-      <c r="T12" t="s">
-        <v>100</v>
-      </c>
-      <c r="U12" t="s">
+      <c r="V12" t="s">
+        <v>109</v>
+      </c>
+      <c r="W12" t="s">
         <v>172</v>
       </c>
-      <c r="V12" t="s">
-        <v>110</v>
-      </c>
-      <c r="W12" t="s">
+      <c r="X12" t="s">
         <v>173</v>
       </c>
-      <c r="X12" t="s">
+      <c r="Y12" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB12" t="s">
         <v>174</v>
       </c>
-      <c r="Y12" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>114</v>
-      </c>
-      <c r="AB12" t="s">
+      <c r="AD12" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE12" t="s">
         <v>175</v>
       </c>
-      <c r="AC12" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>99</v>
-      </c>
       <c r="AG12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AH12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>163</v>
+      </c>
+      <c r="B13" t="s">
         <v>164</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>165</v>
-      </c>
-      <c r="C13" t="s">
-        <v>166</v>
       </c>
       <c r="D13" t="s">
         <v>95</v>
       </c>
       <c r="E13" t="s">
+        <v>166</v>
+      </c>
+      <c r="F13" t="s">
+        <v>99</v>
+      </c>
+      <c r="G13" t="s">
+        <v>99</v>
+      </c>
+      <c r="H13" t="s">
+        <v>99</v>
+      </c>
+      <c r="I13" t="s">
         <v>167</v>
       </c>
-      <c r="F13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G13" t="s">
-        <v>100</v>
-      </c>
-      <c r="H13" t="s">
-        <v>100</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="K13" t="s">
+        <v>99</v>
+      </c>
+      <c r="L13" t="s">
         <v>168</v>
       </c>
-      <c r="J13" t="s">
-        <v>99</v>
-      </c>
-      <c r="K13" t="s">
-        <v>100</v>
-      </c>
-      <c r="L13" t="s">
+      <c r="N13" t="s">
+        <v>99</v>
+      </c>
+      <c r="O13" t="s">
         <v>169</v>
       </c>
-      <c r="M13" t="s">
-        <v>99</v>
-      </c>
-      <c r="N13" t="s">
-        <v>100</v>
-      </c>
-      <c r="O13" t="s">
+      <c r="Q13" t="s">
+        <v>99</v>
+      </c>
+      <c r="R13" t="s">
         <v>170</v>
       </c>
-      <c r="P13" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>100</v>
-      </c>
-      <c r="R13" t="s">
+      <c r="T13" t="s">
+        <v>99</v>
+      </c>
+      <c r="U13" t="s">
         <v>171</v>
       </c>
-      <c r="S13" t="s">
-        <v>99</v>
-      </c>
-      <c r="T13" t="s">
-        <v>100</v>
-      </c>
-      <c r="U13" t="s">
+      <c r="V13" t="s">
+        <v>109</v>
+      </c>
+      <c r="W13" t="s">
         <v>172</v>
       </c>
-      <c r="V13" t="s">
-        <v>110</v>
-      </c>
-      <c r="W13" t="s">
+      <c r="X13" t="s">
         <v>173</v>
       </c>
-      <c r="X13" t="s">
-        <v>174</v>
-      </c>
       <c r="Y13" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA13" t="s">
         <v>113</v>
       </c>
-      <c r="Z13" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>114</v>
-      </c>
       <c r="AB13" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC13" t="s">
         <v>178</v>
       </c>
-      <c r="AC13" t="s">
+      <c r="AD13" t="s">
         <v>179</v>
       </c>
-      <c r="AD13" t="s">
-        <v>180</v>
-      </c>
       <c r="AE13" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AG13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AH13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s">
+        <v>164</v>
+      </c>
+      <c r="C14" t="s">
         <v>165</v>
-      </c>
-      <c r="C14" t="s">
-        <v>166</v>
       </c>
       <c r="D14" t="s">
         <v>95</v>
       </c>
       <c r="E14" t="s">
+        <v>166</v>
+      </c>
+      <c r="F14" t="s">
+        <v>184</v>
+      </c>
+      <c r="G14" t="s">
+        <v>185</v>
+      </c>
+      <c r="H14" t="s">
+        <v>186</v>
+      </c>
+      <c r="I14" t="s">
         <v>167</v>
       </c>
-      <c r="F14" t="s">
-        <v>185</v>
-      </c>
-      <c r="G14" t="s">
-        <v>186</v>
-      </c>
-      <c r="H14" t="s">
-        <v>187</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="K14" t="s">
+        <v>99</v>
+      </c>
+      <c r="L14" t="s">
         <v>168</v>
       </c>
-      <c r="J14" t="s">
-        <v>99</v>
-      </c>
-      <c r="K14" t="s">
-        <v>100</v>
-      </c>
-      <c r="L14" t="s">
+      <c r="N14" t="s">
+        <v>99</v>
+      </c>
+      <c r="O14" t="s">
         <v>169</v>
       </c>
-      <c r="M14" t="s">
-        <v>99</v>
-      </c>
-      <c r="N14" t="s">
-        <v>100</v>
-      </c>
-      <c r="O14" t="s">
+      <c r="Q14" t="s">
+        <v>99</v>
+      </c>
+      <c r="R14" t="s">
         <v>170</v>
       </c>
-      <c r="P14" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>100</v>
-      </c>
-      <c r="R14" t="s">
+      <c r="T14" t="s">
+        <v>99</v>
+      </c>
+      <c r="U14" t="s">
         <v>171</v>
       </c>
-      <c r="S14" t="s">
-        <v>99</v>
-      </c>
-      <c r="T14" t="s">
-        <v>100</v>
-      </c>
-      <c r="U14" t="s">
+      <c r="V14" t="s">
+        <v>109</v>
+      </c>
+      <c r="W14" t="s">
         <v>172</v>
       </c>
-      <c r="V14" t="s">
-        <v>110</v>
-      </c>
-      <c r="W14" t="s">
+      <c r="X14" t="s">
         <v>173</v>
       </c>
-      <c r="X14" t="s">
+      <c r="Y14" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB14" t="s">
         <v>174</v>
       </c>
-      <c r="Y14" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>114</v>
-      </c>
-      <c r="AB14" t="s">
+      <c r="AD14" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE14" t="s">
         <v>175</v>
       </c>
-      <c r="AC14" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE14" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>99</v>
-      </c>
       <c r="AG14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AH14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B15" t="s">
+        <v>164</v>
+      </c>
+      <c r="C15" t="s">
         <v>165</v>
-      </c>
-      <c r="C15" t="s">
-        <v>166</v>
       </c>
       <c r="D15" t="s">
         <v>95</v>
       </c>
       <c r="E15" t="s">
+        <v>166</v>
+      </c>
+      <c r="F15" t="s">
+        <v>184</v>
+      </c>
+      <c r="G15" t="s">
+        <v>185</v>
+      </c>
+      <c r="H15" t="s">
+        <v>186</v>
+      </c>
+      <c r="I15" t="s">
         <v>167</v>
       </c>
-      <c r="F15" t="s">
-        <v>185</v>
-      </c>
-      <c r="G15" t="s">
-        <v>186</v>
-      </c>
-      <c r="H15" t="s">
-        <v>187</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="K15" t="s">
+        <v>99</v>
+      </c>
+      <c r="L15" t="s">
         <v>168</v>
       </c>
-      <c r="J15" t="s">
-        <v>99</v>
-      </c>
-      <c r="K15" t="s">
-        <v>100</v>
-      </c>
-      <c r="L15" t="s">
+      <c r="N15" t="s">
+        <v>99</v>
+      </c>
+      <c r="O15" t="s">
         <v>169</v>
       </c>
-      <c r="M15" t="s">
-        <v>99</v>
-      </c>
-      <c r="N15" t="s">
-        <v>100</v>
-      </c>
-      <c r="O15" t="s">
+      <c r="Q15" t="s">
+        <v>99</v>
+      </c>
+      <c r="R15" t="s">
         <v>170</v>
       </c>
-      <c r="P15" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>100</v>
-      </c>
-      <c r="R15" t="s">
+      <c r="T15" t="s">
+        <v>99</v>
+      </c>
+      <c r="U15" t="s">
         <v>171</v>
       </c>
-      <c r="S15" t="s">
-        <v>99</v>
-      </c>
-      <c r="T15" t="s">
-        <v>100</v>
-      </c>
-      <c r="U15" t="s">
+      <c r="V15" t="s">
+        <v>109</v>
+      </c>
+      <c r="W15" t="s">
         <v>172</v>
       </c>
-      <c r="V15" t="s">
-        <v>110</v>
-      </c>
-      <c r="W15" t="s">
+      <c r="X15" t="s">
         <v>173</v>
       </c>
-      <c r="X15" t="s">
-        <v>174</v>
-      </c>
       <c r="Y15" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA15" t="s">
         <v>113</v>
       </c>
-      <c r="Z15" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>114</v>
-      </c>
       <c r="AB15" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC15" t="s">
         <v>178</v>
       </c>
-      <c r="AC15" t="s">
+      <c r="AD15" t="s">
         <v>179</v>
       </c>
-      <c r="AD15" t="s">
-        <v>180</v>
-      </c>
       <c r="AE15" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AH15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s">
+        <v>164</v>
+      </c>
+      <c r="C16" t="s">
         <v>165</v>
-      </c>
-      <c r="C16" t="s">
-        <v>166</v>
       </c>
       <c r="D16" t="s">
         <v>95</v>
       </c>
       <c r="E16" t="s">
+        <v>166</v>
+      </c>
+      <c r="F16" t="s">
+        <v>184</v>
+      </c>
+      <c r="G16" t="s">
+        <v>185</v>
+      </c>
+      <c r="H16" t="s">
+        <v>186</v>
+      </c>
+      <c r="I16" t="s">
         <v>167</v>
       </c>
-      <c r="F16" t="s">
-        <v>185</v>
-      </c>
-      <c r="G16" t="s">
-        <v>186</v>
-      </c>
-      <c r="H16" t="s">
-        <v>187</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="K16" t="s">
+        <v>99</v>
+      </c>
+      <c r="L16" t="s">
         <v>168</v>
       </c>
-      <c r="J16" t="s">
-        <v>99</v>
-      </c>
-      <c r="K16" t="s">
-        <v>100</v>
-      </c>
-      <c r="L16" t="s">
+      <c r="N16" t="s">
+        <v>99</v>
+      </c>
+      <c r="O16" t="s">
         <v>169</v>
       </c>
-      <c r="M16" t="s">
-        <v>99</v>
-      </c>
-      <c r="N16" t="s">
-        <v>100</v>
-      </c>
-      <c r="O16" t="s">
+      <c r="Q16" t="s">
+        <v>99</v>
+      </c>
+      <c r="R16" t="s">
         <v>170</v>
       </c>
-      <c r="P16" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>100</v>
-      </c>
-      <c r="R16" t="s">
+      <c r="T16" t="s">
+        <v>99</v>
+      </c>
+      <c r="U16" t="s">
         <v>171</v>
       </c>
-      <c r="S16" t="s">
-        <v>99</v>
-      </c>
-      <c r="T16" t="s">
-        <v>100</v>
-      </c>
-      <c r="U16" t="s">
+      <c r="V16" t="s">
+        <v>109</v>
+      </c>
+      <c r="W16" t="s">
         <v>172</v>
       </c>
-      <c r="V16" t="s">
-        <v>110</v>
-      </c>
-      <c r="W16" t="s">
+      <c r="X16" t="s">
         <v>173</v>
       </c>
-      <c r="X16" t="s">
+      <c r="Y16" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB16" t="s">
         <v>174</v>
       </c>
-      <c r="Y16" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>114</v>
-      </c>
-      <c r="AB16" t="s">
+      <c r="AD16" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE16" t="s">
         <v>175</v>
       </c>
-      <c r="AC16" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE16" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>99</v>
-      </c>
       <c r="AG16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AH16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B17" t="s">
+        <v>164</v>
+      </c>
+      <c r="C17" t="s">
         <v>165</v>
-      </c>
-      <c r="C17" t="s">
-        <v>166</v>
       </c>
       <c r="D17" t="s">
         <v>95</v>
       </c>
       <c r="E17" t="s">
+        <v>166</v>
+      </c>
+      <c r="F17" t="s">
+        <v>184</v>
+      </c>
+      <c r="G17" t="s">
+        <v>185</v>
+      </c>
+      <c r="H17" t="s">
+        <v>186</v>
+      </c>
+      <c r="I17" t="s">
         <v>167</v>
       </c>
-      <c r="F17" t="s">
-        <v>185</v>
-      </c>
-      <c r="G17" t="s">
-        <v>186</v>
-      </c>
-      <c r="H17" t="s">
-        <v>187</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="K17" t="s">
+        <v>99</v>
+      </c>
+      <c r="L17" t="s">
         <v>168</v>
       </c>
-      <c r="J17" t="s">
-        <v>99</v>
-      </c>
-      <c r="K17" t="s">
-        <v>100</v>
-      </c>
-      <c r="L17" t="s">
+      <c r="N17" t="s">
+        <v>99</v>
+      </c>
+      <c r="O17" t="s">
         <v>169</v>
       </c>
-      <c r="M17" t="s">
-        <v>99</v>
-      </c>
-      <c r="N17" t="s">
-        <v>100</v>
-      </c>
-      <c r="O17" t="s">
+      <c r="Q17" t="s">
+        <v>99</v>
+      </c>
+      <c r="R17" t="s">
         <v>170</v>
       </c>
-      <c r="P17" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>100</v>
-      </c>
-      <c r="R17" t="s">
+      <c r="T17" t="s">
+        <v>99</v>
+      </c>
+      <c r="U17" t="s">
         <v>171</v>
       </c>
-      <c r="S17" t="s">
-        <v>99</v>
-      </c>
-      <c r="T17" t="s">
-        <v>100</v>
-      </c>
-      <c r="U17" t="s">
+      <c r="V17" t="s">
+        <v>109</v>
+      </c>
+      <c r="W17" t="s">
         <v>172</v>
       </c>
-      <c r="V17" t="s">
-        <v>110</v>
-      </c>
-      <c r="W17" t="s">
+      <c r="X17" t="s">
         <v>173</v>
       </c>
-      <c r="X17" t="s">
-        <v>174</v>
-      </c>
       <c r="Y17" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA17" t="s">
         <v>113</v>
       </c>
-      <c r="Z17" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>114</v>
-      </c>
       <c r="AB17" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC17" t="s">
         <v>178</v>
       </c>
-      <c r="AC17" t="s">
+      <c r="AD17" t="s">
         <v>179</v>
       </c>
-      <c r="AD17" t="s">
-        <v>180</v>
-      </c>
       <c r="AE17" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AG17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AH17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s">
+        <v>164</v>
+      </c>
+      <c r="C18" t="s">
         <v>165</v>
-      </c>
-      <c r="C18" t="s">
-        <v>166</v>
       </c>
       <c r="D18" t="s">
         <v>95</v>
       </c>
       <c r="E18" t="s">
+        <v>166</v>
+      </c>
+      <c r="F18" t="s">
+        <v>184</v>
+      </c>
+      <c r="G18" t="s">
+        <v>185</v>
+      </c>
+      <c r="H18" t="s">
+        <v>186</v>
+      </c>
+      <c r="I18" t="s">
         <v>167</v>
       </c>
-      <c r="F18" t="s">
-        <v>185</v>
-      </c>
-      <c r="G18" t="s">
-        <v>186</v>
-      </c>
-      <c r="H18" t="s">
-        <v>187</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="K18" t="s">
+        <v>99</v>
+      </c>
+      <c r="L18" t="s">
         <v>168</v>
       </c>
-      <c r="J18" t="s">
-        <v>99</v>
-      </c>
-      <c r="K18" t="s">
-        <v>100</v>
-      </c>
-      <c r="L18" t="s">
+      <c r="N18" t="s">
+        <v>99</v>
+      </c>
+      <c r="O18" t="s">
         <v>169</v>
       </c>
-      <c r="M18" t="s">
-        <v>99</v>
-      </c>
-      <c r="N18" t="s">
-        <v>100</v>
-      </c>
-      <c r="O18" t="s">
+      <c r="Q18" t="s">
+        <v>99</v>
+      </c>
+      <c r="R18" t="s">
         <v>170</v>
       </c>
-      <c r="P18" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>100</v>
-      </c>
-      <c r="R18" t="s">
+      <c r="T18" t="s">
+        <v>99</v>
+      </c>
+      <c r="U18" t="s">
         <v>171</v>
       </c>
-      <c r="S18" t="s">
-        <v>99</v>
-      </c>
-      <c r="T18" t="s">
-        <v>100</v>
-      </c>
-      <c r="U18" t="s">
+      <c r="V18" t="s">
+        <v>109</v>
+      </c>
+      <c r="W18" t="s">
         <v>172</v>
       </c>
-      <c r="V18" t="s">
-        <v>110</v>
-      </c>
-      <c r="W18" t="s">
+      <c r="X18" t="s">
         <v>173</v>
       </c>
-      <c r="X18" t="s">
+      <c r="Y18" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB18" t="s">
         <v>174</v>
       </c>
-      <c r="Y18" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>114</v>
-      </c>
-      <c r="AB18" t="s">
+      <c r="AD18" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE18" t="s">
         <v>175</v>
       </c>
-      <c r="AC18" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE18" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>99</v>
-      </c>
       <c r="AG18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AH18" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s">
+        <v>164</v>
+      </c>
+      <c r="C19" t="s">
         <v>165</v>
-      </c>
-      <c r="C19" t="s">
-        <v>166</v>
       </c>
       <c r="D19" t="s">
         <v>95</v>
       </c>
       <c r="E19" t="s">
+        <v>166</v>
+      </c>
+      <c r="F19" t="s">
+        <v>184</v>
+      </c>
+      <c r="G19" t="s">
+        <v>185</v>
+      </c>
+      <c r="H19" t="s">
+        <v>186</v>
+      </c>
+      <c r="I19" t="s">
         <v>167</v>
       </c>
-      <c r="F19" t="s">
-        <v>185</v>
-      </c>
-      <c r="G19" t="s">
-        <v>186</v>
-      </c>
-      <c r="H19" t="s">
-        <v>187</v>
-      </c>
-      <c r="I19" t="s">
+      <c r="K19" t="s">
+        <v>99</v>
+      </c>
+      <c r="L19" t="s">
         <v>168</v>
       </c>
-      <c r="J19" t="s">
-        <v>99</v>
-      </c>
-      <c r="K19" t="s">
-        <v>100</v>
-      </c>
-      <c r="L19" t="s">
+      <c r="N19" t="s">
+        <v>99</v>
+      </c>
+      <c r="O19" t="s">
         <v>169</v>
       </c>
-      <c r="M19" t="s">
-        <v>99</v>
-      </c>
-      <c r="N19" t="s">
-        <v>100</v>
-      </c>
-      <c r="O19" t="s">
+      <c r="Q19" t="s">
+        <v>99</v>
+      </c>
+      <c r="R19" t="s">
         <v>170</v>
       </c>
-      <c r="P19" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>100</v>
-      </c>
-      <c r="R19" t="s">
+      <c r="T19" t="s">
+        <v>99</v>
+      </c>
+      <c r="U19" t="s">
         <v>171</v>
       </c>
-      <c r="S19" t="s">
-        <v>99</v>
-      </c>
-      <c r="T19" t="s">
-        <v>100</v>
-      </c>
-      <c r="U19" t="s">
+      <c r="V19" t="s">
+        <v>109</v>
+      </c>
+      <c r="W19" t="s">
         <v>172</v>
       </c>
-      <c r="V19" t="s">
-        <v>110</v>
-      </c>
-      <c r="W19" t="s">
+      <c r="X19" t="s">
         <v>173</v>
       </c>
-      <c r="X19" t="s">
-        <v>174</v>
-      </c>
       <c r="Y19" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA19" t="s">
         <v>113</v>
       </c>
-      <c r="Z19" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>114</v>
-      </c>
       <c r="AB19" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC19" t="s">
         <v>178</v>
       </c>
-      <c r="AC19" t="s">
+      <c r="AD19" t="s">
         <v>179</v>
       </c>
-      <c r="AD19" t="s">
-        <v>180</v>
-      </c>
       <c r="AE19" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AG19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AH19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s">
+        <v>164</v>
+      </c>
+      <c r="C20" t="s">
         <v>165</v>
-      </c>
-      <c r="C20" t="s">
-        <v>166</v>
       </c>
       <c r="D20" t="s">
         <v>95</v>
       </c>
       <c r="E20" t="s">
+        <v>166</v>
+      </c>
+      <c r="F20" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" t="s">
+        <v>99</v>
+      </c>
+      <c r="I20" t="s">
         <v>167</v>
       </c>
-      <c r="F20" t="s">
-        <v>100</v>
-      </c>
-      <c r="G20" t="s">
-        <v>100</v>
-      </c>
-      <c r="H20" t="s">
-        <v>100</v>
-      </c>
-      <c r="I20" t="s">
+      <c r="K20" t="s">
+        <v>99</v>
+      </c>
+      <c r="L20" t="s">
         <v>168</v>
       </c>
-      <c r="J20" t="s">
-        <v>99</v>
-      </c>
-      <c r="K20" t="s">
-        <v>100</v>
-      </c>
-      <c r="L20" t="s">
+      <c r="N20" t="s">
+        <v>99</v>
+      </c>
+      <c r="O20" t="s">
         <v>169</v>
       </c>
-      <c r="M20" t="s">
-        <v>99</v>
-      </c>
-      <c r="N20" t="s">
-        <v>100</v>
-      </c>
-      <c r="O20" t="s">
+      <c r="Q20" t="s">
+        <v>99</v>
+      </c>
+      <c r="R20" t="s">
         <v>170</v>
       </c>
-      <c r="P20" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>100</v>
-      </c>
-      <c r="R20" t="s">
+      <c r="T20" t="s">
+        <v>99</v>
+      </c>
+      <c r="U20" t="s">
         <v>171</v>
       </c>
-      <c r="S20" t="s">
-        <v>99</v>
-      </c>
-      <c r="T20" t="s">
-        <v>100</v>
-      </c>
-      <c r="U20" t="s">
+      <c r="V20" t="s">
+        <v>109</v>
+      </c>
+      <c r="W20" t="s">
         <v>172</v>
       </c>
-      <c r="V20" t="s">
-        <v>110</v>
-      </c>
-      <c r="W20" t="s">
+      <c r="X20" t="s">
         <v>173</v>
       </c>
-      <c r="X20" t="s">
+      <c r="Y20" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB20" t="s">
         <v>174</v>
       </c>
-      <c r="Y20" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>114</v>
-      </c>
-      <c r="AB20" t="s">
+      <c r="AD20" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE20" t="s">
         <v>175</v>
       </c>
-      <c r="AC20" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE20" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>99</v>
-      </c>
       <c r="AG20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AH20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B21" t="s">
+        <v>164</v>
+      </c>
+      <c r="C21" t="s">
         <v>165</v>
-      </c>
-      <c r="C21" t="s">
-        <v>166</v>
       </c>
       <c r="D21" t="s">
         <v>95</v>
       </c>
       <c r="E21" t="s">
+        <v>166</v>
+      </c>
+      <c r="F21" t="s">
+        <v>99</v>
+      </c>
+      <c r="G21" t="s">
+        <v>99</v>
+      </c>
+      <c r="H21" t="s">
+        <v>99</v>
+      </c>
+      <c r="I21" t="s">
         <v>167</v>
       </c>
-      <c r="F21" t="s">
-        <v>100</v>
-      </c>
-      <c r="G21" t="s">
-        <v>100</v>
-      </c>
-      <c r="H21" t="s">
-        <v>100</v>
-      </c>
-      <c r="I21" t="s">
+      <c r="K21" t="s">
+        <v>99</v>
+      </c>
+      <c r="L21" t="s">
         <v>168</v>
       </c>
-      <c r="J21" t="s">
-        <v>99</v>
-      </c>
-      <c r="K21" t="s">
-        <v>100</v>
-      </c>
-      <c r="L21" t="s">
+      <c r="N21" t="s">
+        <v>99</v>
+      </c>
+      <c r="O21" t="s">
         <v>169</v>
       </c>
-      <c r="M21" t="s">
-        <v>99</v>
-      </c>
-      <c r="N21" t="s">
-        <v>100</v>
-      </c>
-      <c r="O21" t="s">
+      <c r="Q21" t="s">
+        <v>99</v>
+      </c>
+      <c r="R21" t="s">
         <v>170</v>
       </c>
-      <c r="P21" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>100</v>
-      </c>
-      <c r="R21" t="s">
+      <c r="T21" t="s">
+        <v>99</v>
+      </c>
+      <c r="U21" t="s">
         <v>171</v>
       </c>
-      <c r="S21" t="s">
-        <v>99</v>
-      </c>
-      <c r="T21" t="s">
-        <v>100</v>
-      </c>
-      <c r="U21" t="s">
+      <c r="V21" t="s">
+        <v>109</v>
+      </c>
+      <c r="W21" t="s">
         <v>172</v>
       </c>
-      <c r="V21" t="s">
-        <v>110</v>
-      </c>
-      <c r="W21" t="s">
+      <c r="X21" t="s">
         <v>173</v>
       </c>
-      <c r="X21" t="s">
-        <v>174</v>
-      </c>
       <c r="Y21" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA21" t="s">
         <v>113</v>
       </c>
-      <c r="Z21" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>114</v>
-      </c>
       <c r="AB21" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC21" t="s">
         <v>178</v>
       </c>
-      <c r="AC21" t="s">
+      <c r="AD21" t="s">
         <v>179</v>
       </c>
-      <c r="AD21" t="s">
-        <v>180</v>
-      </c>
       <c r="AE21" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AG21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AH21" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -4670,2134 +4233,1894 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AG21"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>55</v>
       </c>
       <c r="B1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" t="s">
         <v>56</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>57</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>58</v>
       </c>
-      <c r="E1" t="s">
-        <v>59</v>
-      </c>
       <c r="F1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G1" t="s">
         <v>205</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>206</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>207</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>208</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>209</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>210</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>211</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>212</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>213</v>
-      </c>
-      <c r="O1" t="s">
-        <v>214</v>
       </c>
       <c r="P1" t="s">
         <v>64</v>
       </c>
       <c r="Q1" t="s">
+        <v>214</v>
+      </c>
+      <c r="R1" t="s">
         <v>215</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>216</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>217</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>218</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>219</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>220</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>221</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>222</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>223</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>224</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>225</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>226</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>227</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>228</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>229</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>230</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E2" t="s">
         <v>166</v>
       </c>
-      <c r="C2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>232</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I2" t="s">
         <v>233</v>
       </c>
-      <c r="G2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L2" t="s">
         <v>234</v>
       </c>
-      <c r="J2" t="s">
-        <v>99</v>
-      </c>
-      <c r="K2" t="s">
-        <v>100</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
+        <v>99</v>
+      </c>
+      <c r="O2" t="s">
         <v>235</v>
       </c>
-      <c r="M2" t="s">
-        <v>99</v>
-      </c>
-      <c r="N2" t="s">
-        <v>100</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>236</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R2" t="s">
         <v>237</v>
       </c>
-      <c r="Q2" t="s">
-        <v>103</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>238</v>
       </c>
-      <c r="S2" t="s">
+      <c r="U2" t="s">
+        <v>99</v>
+      </c>
+      <c r="V2" t="s">
         <v>239</v>
-      </c>
-      <c r="T2" t="s">
-        <v>99</v>
-      </c>
-      <c r="U2" t="s">
-        <v>100</v>
-      </c>
-      <c r="V2" t="s">
-        <v>240</v>
       </c>
       <c r="W2" t="s">
         <v>15</v>
       </c>
       <c r="X2" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y2" t="s">
         <v>241</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>242</v>
       </c>
       <c r="Z2" t="s">
         <v>15</v>
       </c>
       <c r="AA2" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB2" t="s">
         <v>243</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>244</v>
       </c>
       <c r="AC2" t="s">
         <v>15</v>
       </c>
       <c r="AD2" t="s">
+        <v>244</v>
+      </c>
+      <c r="AE2" t="s">
         <v>245</v>
       </c>
-      <c r="AE2" t="s">
-        <v>246</v>
-      </c>
       <c r="AF2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" t="s">
         <v>166</v>
       </c>
-      <c r="C3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>232</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I3" t="s">
         <v>233</v>
       </c>
-      <c r="G3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L3" t="s">
         <v>234</v>
       </c>
-      <c r="J3" t="s">
-        <v>99</v>
-      </c>
-      <c r="K3" t="s">
-        <v>100</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="N3" t="s">
+        <v>99</v>
+      </c>
+      <c r="O3" t="s">
         <v>235</v>
       </c>
-      <c r="M3" t="s">
-        <v>99</v>
-      </c>
-      <c r="N3" t="s">
-        <v>100</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>236</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
+        <v>102</v>
+      </c>
+      <c r="R3" t="s">
         <v>237</v>
       </c>
-      <c r="Q3" t="s">
-        <v>103</v>
-      </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>238</v>
       </c>
-      <c r="S3" t="s">
+      <c r="U3" t="s">
+        <v>99</v>
+      </c>
+      <c r="V3" t="s">
         <v>239</v>
-      </c>
-      <c r="T3" t="s">
-        <v>99</v>
-      </c>
-      <c r="U3" t="s">
-        <v>100</v>
-      </c>
-      <c r="V3" t="s">
-        <v>240</v>
       </c>
       <c r="W3" t="s">
         <v>15</v>
       </c>
       <c r="X3" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y3" t="s">
         <v>241</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>242</v>
       </c>
       <c r="Z3" t="s">
         <v>15</v>
       </c>
       <c r="AA3" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB3" t="s">
         <v>243</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>244</v>
       </c>
       <c r="AC3" t="s">
         <v>15</v>
       </c>
       <c r="AD3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AE3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AF3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" t="s">
         <v>166</v>
       </c>
-      <c r="C4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" t="s">
-        <v>167</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>232</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I4" t="s">
         <v>233</v>
       </c>
-      <c r="G4" t="s">
-        <v>99</v>
-      </c>
-      <c r="H4" t="s">
-        <v>100</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
+        <v>99</v>
+      </c>
+      <c r="L4" t="s">
         <v>234</v>
       </c>
-      <c r="J4" t="s">
-        <v>99</v>
-      </c>
-      <c r="K4" t="s">
-        <v>100</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="N4" t="s">
+        <v>99</v>
+      </c>
+      <c r="O4" t="s">
         <v>235</v>
       </c>
-      <c r="M4" t="s">
-        <v>99</v>
-      </c>
-      <c r="N4" t="s">
-        <v>100</v>
-      </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>236</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
+        <v>102</v>
+      </c>
+      <c r="R4" t="s">
         <v>237</v>
       </c>
-      <c r="Q4" t="s">
-        <v>103</v>
-      </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>238</v>
       </c>
-      <c r="S4" t="s">
+      <c r="U4" t="s">
+        <v>99</v>
+      </c>
+      <c r="V4" t="s">
         <v>239</v>
-      </c>
-      <c r="T4" t="s">
-        <v>99</v>
-      </c>
-      <c r="U4" t="s">
-        <v>100</v>
-      </c>
-      <c r="V4" t="s">
-        <v>240</v>
       </c>
       <c r="W4" t="s">
         <v>15</v>
       </c>
       <c r="X4" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y4" t="s">
         <v>241</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>242</v>
       </c>
       <c r="Z4" t="s">
         <v>15</v>
       </c>
       <c r="AA4" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB4" t="s">
         <v>243</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>244</v>
       </c>
       <c r="AC4" t="s">
         <v>15</v>
       </c>
       <c r="AD4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AE4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AF4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" t="s">
         <v>166</v>
       </c>
-      <c r="C5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5" t="s">
-        <v>167</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>232</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I5" t="s">
         <v>233</v>
       </c>
-      <c r="G5" t="s">
-        <v>99</v>
-      </c>
-      <c r="H5" t="s">
-        <v>100</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="K5" t="s">
+        <v>99</v>
+      </c>
+      <c r="L5" t="s">
         <v>234</v>
       </c>
-      <c r="J5" t="s">
-        <v>99</v>
-      </c>
-      <c r="K5" t="s">
-        <v>100</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="N5" t="s">
+        <v>99</v>
+      </c>
+      <c r="O5" t="s">
         <v>235</v>
       </c>
-      <c r="M5" t="s">
-        <v>99</v>
-      </c>
-      <c r="N5" t="s">
-        <v>100</v>
-      </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>236</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
+        <v>102</v>
+      </c>
+      <c r="R5" t="s">
         <v>237</v>
       </c>
-      <c r="Q5" t="s">
-        <v>103</v>
-      </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>238</v>
       </c>
-      <c r="S5" t="s">
+      <c r="U5" t="s">
+        <v>99</v>
+      </c>
+      <c r="V5" t="s">
         <v>239</v>
-      </c>
-      <c r="T5" t="s">
-        <v>99</v>
-      </c>
-      <c r="U5" t="s">
-        <v>100</v>
-      </c>
-      <c r="V5" t="s">
-        <v>240</v>
       </c>
       <c r="W5" t="s">
         <v>15</v>
       </c>
       <c r="X5" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y5" t="s">
         <v>241</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>242</v>
       </c>
       <c r="Z5" t="s">
         <v>15</v>
       </c>
       <c r="AA5" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB5" t="s">
         <v>243</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>244</v>
       </c>
       <c r="AC5" t="s">
         <v>15</v>
       </c>
       <c r="AD5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AE5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AF5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" t="s">
         <v>166</v>
       </c>
-      <c r="C6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6" t="s">
-        <v>167</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>232</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
+        <v>99</v>
+      </c>
+      <c r="I6" t="s">
         <v>233</v>
       </c>
-      <c r="G6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H6" t="s">
-        <v>100</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="K6" t="s">
+        <v>99</v>
+      </c>
+      <c r="L6" t="s">
         <v>234</v>
       </c>
-      <c r="J6" t="s">
-        <v>99</v>
-      </c>
-      <c r="K6" t="s">
-        <v>100</v>
-      </c>
-      <c r="L6" t="s">
+      <c r="N6" t="s">
+        <v>99</v>
+      </c>
+      <c r="O6" t="s">
         <v>235</v>
       </c>
-      <c r="M6" t="s">
-        <v>99</v>
-      </c>
-      <c r="N6" t="s">
-        <v>100</v>
-      </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>236</v>
       </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
+        <v>102</v>
+      </c>
+      <c r="R6" t="s">
         <v>237</v>
       </c>
-      <c r="Q6" t="s">
-        <v>103</v>
-      </c>
-      <c r="R6" t="s">
+      <c r="S6" t="s">
         <v>238</v>
       </c>
-      <c r="S6" t="s">
+      <c r="U6" t="s">
+        <v>99</v>
+      </c>
+      <c r="V6" t="s">
         <v>239</v>
-      </c>
-      <c r="T6" t="s">
-        <v>99</v>
-      </c>
-      <c r="U6" t="s">
-        <v>100</v>
-      </c>
-      <c r="V6" t="s">
-        <v>240</v>
       </c>
       <c r="W6" t="s">
         <v>15</v>
       </c>
       <c r="X6" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y6" t="s">
         <v>241</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>242</v>
       </c>
       <c r="Z6" t="s">
         <v>15</v>
       </c>
       <c r="AA6" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB6" t="s">
         <v>243</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>244</v>
       </c>
       <c r="AC6" t="s">
         <v>15</v>
       </c>
       <c r="AD6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AE6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AF6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" t="s">
         <v>166</v>
       </c>
-      <c r="C7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>232</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I7" t="s">
         <v>233</v>
       </c>
-      <c r="G7" t="s">
-        <v>99</v>
-      </c>
-      <c r="H7" t="s">
-        <v>100</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="K7" t="s">
+        <v>99</v>
+      </c>
+      <c r="L7" t="s">
         <v>234</v>
       </c>
-      <c r="J7" t="s">
-        <v>99</v>
-      </c>
-      <c r="K7" t="s">
-        <v>100</v>
-      </c>
-      <c r="L7" t="s">
+      <c r="N7" t="s">
+        <v>99</v>
+      </c>
+      <c r="O7" t="s">
         <v>235</v>
       </c>
-      <c r="M7" t="s">
-        <v>99</v>
-      </c>
-      <c r="N7" t="s">
-        <v>100</v>
-      </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>236</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
+        <v>102</v>
+      </c>
+      <c r="R7" t="s">
         <v>237</v>
       </c>
-      <c r="Q7" t="s">
-        <v>103</v>
-      </c>
-      <c r="R7" t="s">
+      <c r="S7" t="s">
         <v>238</v>
       </c>
-      <c r="S7" t="s">
+      <c r="U7" t="s">
+        <v>99</v>
+      </c>
+      <c r="V7" t="s">
         <v>239</v>
-      </c>
-      <c r="T7" t="s">
-        <v>99</v>
-      </c>
-      <c r="U7" t="s">
-        <v>100</v>
-      </c>
-      <c r="V7" t="s">
-        <v>240</v>
       </c>
       <c r="W7" t="s">
         <v>15</v>
       </c>
       <c r="X7" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y7" t="s">
         <v>241</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>242</v>
       </c>
       <c r="Z7" t="s">
         <v>15</v>
       </c>
       <c r="AA7" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB7" t="s">
         <v>243</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>244</v>
       </c>
       <c r="AC7" t="s">
         <v>15</v>
       </c>
       <c r="AD7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AE7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AF7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B8" t="s">
+        <v>231</v>
+      </c>
+      <c r="C8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" t="s">
         <v>166</v>
       </c>
-      <c r="C8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" t="s">
-        <v>167</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>232</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
+        <v>99</v>
+      </c>
+      <c r="I8" t="s">
         <v>233</v>
       </c>
-      <c r="G8" t="s">
-        <v>99</v>
-      </c>
-      <c r="H8" t="s">
-        <v>100</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="K8" t="s">
+        <v>99</v>
+      </c>
+      <c r="L8" t="s">
         <v>234</v>
       </c>
-      <c r="J8" t="s">
-        <v>99</v>
-      </c>
-      <c r="K8" t="s">
-        <v>100</v>
-      </c>
-      <c r="L8" t="s">
+      <c r="N8" t="s">
+        <v>99</v>
+      </c>
+      <c r="O8" t="s">
         <v>235</v>
       </c>
-      <c r="M8" t="s">
-        <v>99</v>
-      </c>
-      <c r="N8" t="s">
-        <v>100</v>
-      </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>236</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
+        <v>102</v>
+      </c>
+      <c r="R8" t="s">
         <v>237</v>
       </c>
-      <c r="Q8" t="s">
-        <v>103</v>
-      </c>
-      <c r="R8" t="s">
+      <c r="S8" t="s">
         <v>238</v>
       </c>
-      <c r="S8" t="s">
+      <c r="U8" t="s">
+        <v>99</v>
+      </c>
+      <c r="V8" t="s">
         <v>239</v>
-      </c>
-      <c r="T8" t="s">
-        <v>99</v>
-      </c>
-      <c r="U8" t="s">
-        <v>100</v>
-      </c>
-      <c r="V8" t="s">
-        <v>240</v>
       </c>
       <c r="W8" t="s">
         <v>15</v>
       </c>
       <c r="X8" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y8" t="s">
         <v>241</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>242</v>
       </c>
       <c r="Z8" t="s">
         <v>15</v>
       </c>
       <c r="AA8" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB8" t="s">
         <v>243</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>244</v>
       </c>
       <c r="AC8" t="s">
         <v>15</v>
       </c>
       <c r="AD8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AE8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AF8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B9" t="s">
+        <v>231</v>
+      </c>
+      <c r="C9" t="s">
+        <v>165</v>
+      </c>
+      <c r="D9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9" t="s">
         <v>166</v>
       </c>
-      <c r="C9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" t="s">
-        <v>167</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>232</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
+        <v>99</v>
+      </c>
+      <c r="I9" t="s">
         <v>233</v>
       </c>
-      <c r="G9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H9" t="s">
-        <v>100</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="K9" t="s">
+        <v>99</v>
+      </c>
+      <c r="L9" t="s">
         <v>234</v>
       </c>
-      <c r="J9" t="s">
-        <v>99</v>
-      </c>
-      <c r="K9" t="s">
-        <v>100</v>
-      </c>
-      <c r="L9" t="s">
+      <c r="N9" t="s">
+        <v>99</v>
+      </c>
+      <c r="O9" t="s">
         <v>235</v>
       </c>
-      <c r="M9" t="s">
-        <v>99</v>
-      </c>
-      <c r="N9" t="s">
-        <v>100</v>
-      </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>236</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
+        <v>102</v>
+      </c>
+      <c r="R9" t="s">
         <v>237</v>
       </c>
-      <c r="Q9" t="s">
-        <v>103</v>
-      </c>
-      <c r="R9" t="s">
+      <c r="S9" t="s">
         <v>238</v>
       </c>
-      <c r="S9" t="s">
+      <c r="U9" t="s">
+        <v>99</v>
+      </c>
+      <c r="V9" t="s">
         <v>239</v>
-      </c>
-      <c r="T9" t="s">
-        <v>99</v>
-      </c>
-      <c r="U9" t="s">
-        <v>100</v>
-      </c>
-      <c r="V9" t="s">
-        <v>240</v>
       </c>
       <c r="W9" t="s">
         <v>15</v>
       </c>
       <c r="X9" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y9" t="s">
         <v>241</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>242</v>
       </c>
       <c r="Z9" t="s">
         <v>15</v>
       </c>
       <c r="AA9" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB9" t="s">
         <v>243</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>244</v>
       </c>
       <c r="AC9" t="s">
         <v>15</v>
       </c>
       <c r="AD9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AE9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AF9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C10" t="s">
+        <v>165</v>
+      </c>
+      <c r="D10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" t="s">
         <v>166</v>
       </c>
-      <c r="C10" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" t="s">
-        <v>167</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>232</v>
       </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I10" t="s">
         <v>233</v>
       </c>
-      <c r="G10" t="s">
-        <v>99</v>
-      </c>
-      <c r="H10" t="s">
-        <v>100</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="K10" t="s">
+        <v>99</v>
+      </c>
+      <c r="L10" t="s">
         <v>234</v>
       </c>
-      <c r="J10" t="s">
-        <v>99</v>
-      </c>
-      <c r="K10" t="s">
-        <v>100</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="N10" t="s">
+        <v>99</v>
+      </c>
+      <c r="O10" t="s">
         <v>235</v>
       </c>
-      <c r="M10" t="s">
-        <v>99</v>
-      </c>
-      <c r="N10" t="s">
-        <v>100</v>
-      </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>236</v>
       </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
+        <v>102</v>
+      </c>
+      <c r="R10" t="s">
         <v>237</v>
       </c>
-      <c r="Q10" t="s">
-        <v>103</v>
-      </c>
-      <c r="R10" t="s">
+      <c r="S10" t="s">
         <v>238</v>
       </c>
-      <c r="S10" t="s">
+      <c r="U10" t="s">
+        <v>99</v>
+      </c>
+      <c r="V10" t="s">
         <v>239</v>
-      </c>
-      <c r="T10" t="s">
-        <v>99</v>
-      </c>
-      <c r="U10" t="s">
-        <v>100</v>
-      </c>
-      <c r="V10" t="s">
-        <v>240</v>
       </c>
       <c r="W10" t="s">
         <v>15</v>
       </c>
       <c r="X10" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y10" t="s">
         <v>241</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>242</v>
       </c>
       <c r="Z10" t="s">
         <v>15</v>
       </c>
       <c r="AA10" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB10" t="s">
         <v>243</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>244</v>
       </c>
       <c r="AC10" t="s">
         <v>15</v>
       </c>
       <c r="AD10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AE10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AF10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B11" t="s">
+        <v>231</v>
+      </c>
+      <c r="C11" t="s">
+        <v>165</v>
+      </c>
+      <c r="D11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E11" t="s">
         <v>166</v>
       </c>
-      <c r="C11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D11" t="s">
-        <v>167</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>232</v>
       </c>
-      <c r="F11" t="s">
+      <c r="H11" t="s">
+        <v>99</v>
+      </c>
+      <c r="I11" t="s">
         <v>233</v>
       </c>
-      <c r="G11" t="s">
-        <v>99</v>
-      </c>
-      <c r="H11" t="s">
-        <v>100</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="K11" t="s">
+        <v>99</v>
+      </c>
+      <c r="L11" t="s">
         <v>234</v>
       </c>
-      <c r="J11" t="s">
-        <v>99</v>
-      </c>
-      <c r="K11" t="s">
-        <v>100</v>
-      </c>
-      <c r="L11" t="s">
+      <c r="N11" t="s">
+        <v>99</v>
+      </c>
+      <c r="O11" t="s">
         <v>235</v>
       </c>
-      <c r="M11" t="s">
-        <v>99</v>
-      </c>
-      <c r="N11" t="s">
-        <v>100</v>
-      </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>236</v>
       </c>
-      <c r="P11" t="s">
+      <c r="Q11" t="s">
+        <v>102</v>
+      </c>
+      <c r="R11" t="s">
         <v>237</v>
       </c>
-      <c r="Q11" t="s">
-        <v>103</v>
-      </c>
-      <c r="R11" t="s">
+      <c r="S11" t="s">
         <v>238</v>
       </c>
-      <c r="S11" t="s">
+      <c r="U11" t="s">
+        <v>99</v>
+      </c>
+      <c r="V11" t="s">
         <v>239</v>
-      </c>
-      <c r="T11" t="s">
-        <v>99</v>
-      </c>
-      <c r="U11" t="s">
-        <v>100</v>
-      </c>
-      <c r="V11" t="s">
-        <v>240</v>
       </c>
       <c r="W11" t="s">
         <v>15</v>
       </c>
       <c r="X11" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y11" t="s">
         <v>241</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>242</v>
       </c>
       <c r="Z11" t="s">
         <v>15</v>
       </c>
       <c r="AA11" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB11" t="s">
         <v>243</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>244</v>
       </c>
       <c r="AC11" t="s">
         <v>15</v>
       </c>
       <c r="AD11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AE11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AF11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B12" t="s">
+        <v>231</v>
+      </c>
+      <c r="C12" t="s">
+        <v>165</v>
+      </c>
+      <c r="D12" t="s">
+        <v>95</v>
+      </c>
+      <c r="E12" t="s">
         <v>166</v>
       </c>
-      <c r="C12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D12" t="s">
-        <v>167</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>232</v>
       </c>
-      <c r="F12" t="s">
+      <c r="H12" t="s">
+        <v>99</v>
+      </c>
+      <c r="I12" t="s">
         <v>233</v>
       </c>
-      <c r="G12" t="s">
-        <v>99</v>
-      </c>
-      <c r="H12" t="s">
-        <v>100</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="K12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L12" t="s">
         <v>234</v>
       </c>
-      <c r="J12" t="s">
-        <v>99</v>
-      </c>
-      <c r="K12" t="s">
-        <v>100</v>
-      </c>
-      <c r="L12" t="s">
+      <c r="N12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O12" t="s">
         <v>235</v>
       </c>
-      <c r="M12" t="s">
-        <v>99</v>
-      </c>
-      <c r="N12" t="s">
-        <v>100</v>
-      </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>236</v>
       </c>
-      <c r="P12" t="s">
+      <c r="Q12" t="s">
+        <v>102</v>
+      </c>
+      <c r="R12" t="s">
         <v>237</v>
       </c>
-      <c r="Q12" t="s">
-        <v>103</v>
-      </c>
-      <c r="R12" t="s">
+      <c r="S12" t="s">
         <v>238</v>
       </c>
-      <c r="S12" t="s">
+      <c r="U12" t="s">
+        <v>99</v>
+      </c>
+      <c r="V12" t="s">
         <v>239</v>
-      </c>
-      <c r="T12" t="s">
-        <v>99</v>
-      </c>
-      <c r="U12" t="s">
-        <v>100</v>
-      </c>
-      <c r="V12" t="s">
-        <v>240</v>
       </c>
       <c r="W12" t="s">
         <v>15</v>
       </c>
       <c r="X12" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y12" t="s">
         <v>241</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>242</v>
       </c>
       <c r="Z12" t="s">
         <v>15</v>
       </c>
       <c r="AA12" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB12" t="s">
         <v>243</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>244</v>
       </c>
       <c r="AC12" t="s">
         <v>15</v>
       </c>
       <c r="AD12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AE12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AF12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B13" t="s">
+        <v>231</v>
+      </c>
+      <c r="C13" t="s">
+        <v>165</v>
+      </c>
+      <c r="D13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" t="s">
         <v>166</v>
       </c>
-      <c r="C13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D13" t="s">
-        <v>167</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>232</v>
       </c>
-      <c r="F13" t="s">
+      <c r="H13" t="s">
+        <v>99</v>
+      </c>
+      <c r="I13" t="s">
         <v>233</v>
       </c>
-      <c r="G13" t="s">
-        <v>99</v>
-      </c>
-      <c r="H13" t="s">
-        <v>100</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="K13" t="s">
+        <v>99</v>
+      </c>
+      <c r="L13" t="s">
         <v>234</v>
       </c>
-      <c r="J13" t="s">
-        <v>99</v>
-      </c>
-      <c r="K13" t="s">
-        <v>100</v>
-      </c>
-      <c r="L13" t="s">
+      <c r="N13" t="s">
+        <v>99</v>
+      </c>
+      <c r="O13" t="s">
         <v>235</v>
       </c>
-      <c r="M13" t="s">
-        <v>99</v>
-      </c>
-      <c r="N13" t="s">
-        <v>100</v>
-      </c>
-      <c r="O13" t="s">
+      <c r="P13" t="s">
         <v>236</v>
       </c>
-      <c r="P13" t="s">
+      <c r="Q13" t="s">
+        <v>102</v>
+      </c>
+      <c r="R13" t="s">
         <v>237</v>
       </c>
-      <c r="Q13" t="s">
-        <v>103</v>
-      </c>
-      <c r="R13" t="s">
+      <c r="S13" t="s">
         <v>238</v>
       </c>
-      <c r="S13" t="s">
+      <c r="U13" t="s">
+        <v>99</v>
+      </c>
+      <c r="V13" t="s">
         <v>239</v>
-      </c>
-      <c r="T13" t="s">
-        <v>99</v>
-      </c>
-      <c r="U13" t="s">
-        <v>100</v>
-      </c>
-      <c r="V13" t="s">
-        <v>240</v>
       </c>
       <c r="W13" t="s">
         <v>15</v>
       </c>
       <c r="X13" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y13" t="s">
         <v>241</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>242</v>
       </c>
       <c r="Z13" t="s">
         <v>15</v>
       </c>
       <c r="AA13" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB13" t="s">
         <v>243</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>244</v>
       </c>
       <c r="AC13" t="s">
         <v>15</v>
       </c>
       <c r="AD13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AE13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AF13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B14" t="s">
+        <v>231</v>
+      </c>
+      <c r="C14" t="s">
+        <v>165</v>
+      </c>
+      <c r="D14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" t="s">
         <v>166</v>
       </c>
-      <c r="C14" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" t="s">
-        <v>167</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>232</v>
       </c>
-      <c r="F14" t="s">
+      <c r="H14" t="s">
+        <v>99</v>
+      </c>
+      <c r="I14" t="s">
         <v>233</v>
       </c>
-      <c r="G14" t="s">
-        <v>99</v>
-      </c>
-      <c r="H14" t="s">
-        <v>100</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="K14" t="s">
+        <v>99</v>
+      </c>
+      <c r="L14" t="s">
         <v>234</v>
       </c>
-      <c r="J14" t="s">
-        <v>99</v>
-      </c>
-      <c r="K14" t="s">
-        <v>100</v>
-      </c>
-      <c r="L14" t="s">
+      <c r="N14" t="s">
+        <v>99</v>
+      </c>
+      <c r="O14" t="s">
         <v>235</v>
       </c>
-      <c r="M14" t="s">
-        <v>99</v>
-      </c>
-      <c r="N14" t="s">
-        <v>100</v>
-      </c>
-      <c r="O14" t="s">
+      <c r="P14" t="s">
         <v>236</v>
       </c>
-      <c r="P14" t="s">
+      <c r="Q14" t="s">
+        <v>102</v>
+      </c>
+      <c r="R14" t="s">
         <v>237</v>
       </c>
-      <c r="Q14" t="s">
-        <v>103</v>
-      </c>
-      <c r="R14" t="s">
+      <c r="S14" t="s">
         <v>238</v>
       </c>
-      <c r="S14" t="s">
+      <c r="U14" t="s">
+        <v>99</v>
+      </c>
+      <c r="V14" t="s">
         <v>239</v>
-      </c>
-      <c r="T14" t="s">
-        <v>99</v>
-      </c>
-      <c r="U14" t="s">
-        <v>100</v>
-      </c>
-      <c r="V14" t="s">
-        <v>240</v>
       </c>
       <c r="W14" t="s">
         <v>15</v>
       </c>
       <c r="X14" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y14" t="s">
         <v>241</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>242</v>
       </c>
       <c r="Z14" t="s">
         <v>15</v>
       </c>
       <c r="AA14" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB14" t="s">
         <v>243</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>244</v>
       </c>
       <c r="AC14" t="s">
         <v>15</v>
       </c>
       <c r="AD14" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AE14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AF14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B15" t="s">
+        <v>231</v>
+      </c>
+      <c r="C15" t="s">
+        <v>165</v>
+      </c>
+      <c r="D15" t="s">
+        <v>95</v>
+      </c>
+      <c r="E15" t="s">
         <v>166</v>
       </c>
-      <c r="C15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" t="s">
-        <v>167</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>232</v>
       </c>
-      <c r="F15" t="s">
+      <c r="H15" t="s">
+        <v>99</v>
+      </c>
+      <c r="I15" t="s">
         <v>233</v>
       </c>
-      <c r="G15" t="s">
-        <v>99</v>
-      </c>
-      <c r="H15" t="s">
-        <v>100</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="K15" t="s">
+        <v>99</v>
+      </c>
+      <c r="L15" t="s">
         <v>234</v>
       </c>
-      <c r="J15" t="s">
-        <v>99</v>
-      </c>
-      <c r="K15" t="s">
-        <v>100</v>
-      </c>
-      <c r="L15" t="s">
+      <c r="N15" t="s">
+        <v>99</v>
+      </c>
+      <c r="O15" t="s">
         <v>235</v>
       </c>
-      <c r="M15" t="s">
-        <v>99</v>
-      </c>
-      <c r="N15" t="s">
-        <v>100</v>
-      </c>
-      <c r="O15" t="s">
+      <c r="P15" t="s">
         <v>236</v>
       </c>
-      <c r="P15" t="s">
+      <c r="Q15" t="s">
+        <v>102</v>
+      </c>
+      <c r="R15" t="s">
         <v>237</v>
       </c>
-      <c r="Q15" t="s">
-        <v>103</v>
-      </c>
-      <c r="R15" t="s">
+      <c r="S15" t="s">
         <v>238</v>
       </c>
-      <c r="S15" t="s">
+      <c r="U15" t="s">
+        <v>99</v>
+      </c>
+      <c r="V15" t="s">
         <v>239</v>
-      </c>
-      <c r="T15" t="s">
-        <v>99</v>
-      </c>
-      <c r="U15" t="s">
-        <v>100</v>
-      </c>
-      <c r="V15" t="s">
-        <v>240</v>
       </c>
       <c r="W15" t="s">
         <v>15</v>
       </c>
       <c r="X15" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y15" t="s">
         <v>241</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>242</v>
       </c>
       <c r="Z15" t="s">
         <v>15</v>
       </c>
       <c r="AA15" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB15" t="s">
         <v>243</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>244</v>
       </c>
       <c r="AC15" t="s">
         <v>15</v>
       </c>
       <c r="AD15" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AE15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AF15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B16" t="s">
+        <v>231</v>
+      </c>
+      <c r="C16" t="s">
+        <v>165</v>
+      </c>
+      <c r="D16" t="s">
+        <v>95</v>
+      </c>
+      <c r="E16" t="s">
         <v>166</v>
       </c>
-      <c r="C16" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" t="s">
-        <v>167</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>232</v>
       </c>
-      <c r="F16" t="s">
+      <c r="H16" t="s">
+        <v>99</v>
+      </c>
+      <c r="I16" t="s">
         <v>233</v>
       </c>
-      <c r="G16" t="s">
-        <v>99</v>
-      </c>
-      <c r="H16" t="s">
-        <v>100</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="K16" t="s">
+        <v>99</v>
+      </c>
+      <c r="L16" t="s">
         <v>234</v>
       </c>
-      <c r="J16" t="s">
-        <v>99</v>
-      </c>
-      <c r="K16" t="s">
-        <v>100</v>
-      </c>
-      <c r="L16" t="s">
+      <c r="N16" t="s">
+        <v>99</v>
+      </c>
+      <c r="O16" t="s">
         <v>235</v>
       </c>
-      <c r="M16" t="s">
-        <v>99</v>
-      </c>
-      <c r="N16" t="s">
-        <v>100</v>
-      </c>
-      <c r="O16" t="s">
+      <c r="P16" t="s">
         <v>236</v>
       </c>
-      <c r="P16" t="s">
+      <c r="Q16" t="s">
+        <v>102</v>
+      </c>
+      <c r="R16" t="s">
         <v>237</v>
       </c>
-      <c r="Q16" t="s">
-        <v>103</v>
-      </c>
-      <c r="R16" t="s">
+      <c r="S16" t="s">
         <v>238</v>
       </c>
-      <c r="S16" t="s">
+      <c r="U16" t="s">
+        <v>99</v>
+      </c>
+      <c r="V16" t="s">
         <v>239</v>
-      </c>
-      <c r="T16" t="s">
-        <v>99</v>
-      </c>
-      <c r="U16" t="s">
-        <v>100</v>
-      </c>
-      <c r="V16" t="s">
-        <v>240</v>
       </c>
       <c r="W16" t="s">
         <v>15</v>
       </c>
       <c r="X16" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y16" t="s">
         <v>241</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>242</v>
       </c>
       <c r="Z16" t="s">
         <v>15</v>
       </c>
       <c r="AA16" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB16" t="s">
         <v>243</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>244</v>
       </c>
       <c r="AC16" t="s">
         <v>15</v>
       </c>
       <c r="AD16" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AE16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AF16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s">
+        <v>231</v>
+      </c>
+      <c r="C17" t="s">
+        <v>165</v>
+      </c>
+      <c r="D17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" t="s">
         <v>166</v>
       </c>
-      <c r="C17" t="s">
-        <v>95</v>
-      </c>
-      <c r="D17" t="s">
-        <v>167</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>232</v>
       </c>
-      <c r="F17" t="s">
+      <c r="H17" t="s">
+        <v>99</v>
+      </c>
+      <c r="I17" t="s">
         <v>233</v>
       </c>
-      <c r="G17" t="s">
-        <v>99</v>
-      </c>
-      <c r="H17" t="s">
-        <v>100</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="K17" t="s">
+        <v>99</v>
+      </c>
+      <c r="L17" t="s">
         <v>234</v>
       </c>
-      <c r="J17" t="s">
-        <v>99</v>
-      </c>
-      <c r="K17" t="s">
-        <v>100</v>
-      </c>
-      <c r="L17" t="s">
+      <c r="N17" t="s">
+        <v>99</v>
+      </c>
+      <c r="O17" t="s">
         <v>235</v>
       </c>
-      <c r="M17" t="s">
-        <v>99</v>
-      </c>
-      <c r="N17" t="s">
-        <v>100</v>
-      </c>
-      <c r="O17" t="s">
+      <c r="P17" t="s">
         <v>236</v>
       </c>
-      <c r="P17" t="s">
+      <c r="Q17" t="s">
+        <v>102</v>
+      </c>
+      <c r="R17" t="s">
         <v>237</v>
       </c>
-      <c r="Q17" t="s">
-        <v>103</v>
-      </c>
-      <c r="R17" t="s">
+      <c r="S17" t="s">
         <v>238</v>
       </c>
-      <c r="S17" t="s">
+      <c r="U17" t="s">
+        <v>99</v>
+      </c>
+      <c r="V17" t="s">
         <v>239</v>
-      </c>
-      <c r="T17" t="s">
-        <v>99</v>
-      </c>
-      <c r="U17" t="s">
-        <v>100</v>
-      </c>
-      <c r="V17" t="s">
-        <v>240</v>
       </c>
       <c r="W17" t="s">
         <v>15</v>
       </c>
       <c r="X17" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y17" t="s">
         <v>241</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>242</v>
       </c>
       <c r="Z17" t="s">
         <v>15</v>
       </c>
       <c r="AA17" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB17" t="s">
         <v>243</v>
-      </c>
-      <c r="AB17" t="s">
-        <v>244</v>
       </c>
       <c r="AC17" t="s">
         <v>15</v>
       </c>
       <c r="AD17" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AE17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AF17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C18" t="s">
+        <v>165</v>
+      </c>
+      <c r="D18" t="s">
+        <v>95</v>
+      </c>
+      <c r="E18" t="s">
         <v>166</v>
       </c>
-      <c r="C18" t="s">
-        <v>95</v>
-      </c>
-      <c r="D18" t="s">
-        <v>167</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>232</v>
       </c>
-      <c r="F18" t="s">
+      <c r="H18" t="s">
+        <v>99</v>
+      </c>
+      <c r="I18" t="s">
         <v>233</v>
       </c>
-      <c r="G18" t="s">
-        <v>99</v>
-      </c>
-      <c r="H18" t="s">
-        <v>100</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="K18" t="s">
+        <v>99</v>
+      </c>
+      <c r="L18" t="s">
         <v>234</v>
       </c>
-      <c r="J18" t="s">
-        <v>99</v>
-      </c>
-      <c r="K18" t="s">
-        <v>100</v>
-      </c>
-      <c r="L18" t="s">
+      <c r="N18" t="s">
+        <v>99</v>
+      </c>
+      <c r="O18" t="s">
         <v>235</v>
       </c>
-      <c r="M18" t="s">
-        <v>99</v>
-      </c>
-      <c r="N18" t="s">
-        <v>100</v>
-      </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
         <v>236</v>
       </c>
-      <c r="P18" t="s">
+      <c r="Q18" t="s">
+        <v>102</v>
+      </c>
+      <c r="R18" t="s">
         <v>237</v>
       </c>
-      <c r="Q18" t="s">
-        <v>103</v>
-      </c>
-      <c r="R18" t="s">
+      <c r="S18" t="s">
         <v>238</v>
       </c>
-      <c r="S18" t="s">
+      <c r="U18" t="s">
+        <v>99</v>
+      </c>
+      <c r="V18" t="s">
         <v>239</v>
-      </c>
-      <c r="T18" t="s">
-        <v>99</v>
-      </c>
-      <c r="U18" t="s">
-        <v>100</v>
-      </c>
-      <c r="V18" t="s">
-        <v>240</v>
       </c>
       <c r="W18" t="s">
         <v>15</v>
       </c>
       <c r="X18" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y18" t="s">
         <v>241</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>242</v>
       </c>
       <c r="Z18" t="s">
         <v>15</v>
       </c>
       <c r="AA18" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB18" t="s">
         <v>243</v>
-      </c>
-      <c r="AB18" t="s">
-        <v>244</v>
       </c>
       <c r="AC18" t="s">
         <v>15</v>
       </c>
       <c r="AD18" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AE18" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AF18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s">
+        <v>231</v>
+      </c>
+      <c r="C19" t="s">
+        <v>165</v>
+      </c>
+      <c r="D19" t="s">
+        <v>95</v>
+      </c>
+      <c r="E19" t="s">
         <v>166</v>
       </c>
-      <c r="C19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>232</v>
       </c>
-      <c r="F19" t="s">
+      <c r="H19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I19" t="s">
         <v>233</v>
       </c>
-      <c r="G19" t="s">
-        <v>99</v>
-      </c>
-      <c r="H19" t="s">
-        <v>100</v>
-      </c>
-      <c r="I19" t="s">
+      <c r="K19" t="s">
+        <v>99</v>
+      </c>
+      <c r="L19" t="s">
         <v>234</v>
       </c>
-      <c r="J19" t="s">
-        <v>99</v>
-      </c>
-      <c r="K19" t="s">
-        <v>100</v>
-      </c>
-      <c r="L19" t="s">
+      <c r="N19" t="s">
+        <v>99</v>
+      </c>
+      <c r="O19" t="s">
         <v>235</v>
       </c>
-      <c r="M19" t="s">
-        <v>99</v>
-      </c>
-      <c r="N19" t="s">
-        <v>100</v>
-      </c>
-      <c r="O19" t="s">
+      <c r="P19" t="s">
         <v>236</v>
       </c>
-      <c r="P19" t="s">
+      <c r="Q19" t="s">
+        <v>102</v>
+      </c>
+      <c r="R19" t="s">
         <v>237</v>
       </c>
-      <c r="Q19" t="s">
-        <v>103</v>
-      </c>
-      <c r="R19" t="s">
+      <c r="S19" t="s">
         <v>238</v>
       </c>
-      <c r="S19" t="s">
+      <c r="U19" t="s">
+        <v>99</v>
+      </c>
+      <c r="V19" t="s">
         <v>239</v>
-      </c>
-      <c r="T19" t="s">
-        <v>99</v>
-      </c>
-      <c r="U19" t="s">
-        <v>100</v>
-      </c>
-      <c r="V19" t="s">
-        <v>240</v>
       </c>
       <c r="W19" t="s">
         <v>15</v>
       </c>
       <c r="X19" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y19" t="s">
         <v>241</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>242</v>
       </c>
       <c r="Z19" t="s">
         <v>15</v>
       </c>
       <c r="AA19" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB19" t="s">
         <v>243</v>
-      </c>
-      <c r="AB19" t="s">
-        <v>244</v>
       </c>
       <c r="AC19" t="s">
         <v>15</v>
       </c>
       <c r="AD19" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AE19" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AF19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s">
+        <v>231</v>
+      </c>
+      <c r="C20" t="s">
+        <v>165</v>
+      </c>
+      <c r="D20" t="s">
+        <v>95</v>
+      </c>
+      <c r="E20" t="s">
         <v>166</v>
       </c>
-      <c r="C20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" t="s">
-        <v>167</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>232</v>
       </c>
-      <c r="F20" t="s">
+      <c r="H20" t="s">
+        <v>99</v>
+      </c>
+      <c r="I20" t="s">
         <v>233</v>
       </c>
-      <c r="G20" t="s">
-        <v>99</v>
-      </c>
-      <c r="H20" t="s">
-        <v>100</v>
-      </c>
-      <c r="I20" t="s">
+      <c r="K20" t="s">
+        <v>99</v>
+      </c>
+      <c r="L20" t="s">
         <v>234</v>
       </c>
-      <c r="J20" t="s">
-        <v>99</v>
-      </c>
-      <c r="K20" t="s">
-        <v>100</v>
-      </c>
-      <c r="L20" t="s">
+      <c r="N20" t="s">
+        <v>99</v>
+      </c>
+      <c r="O20" t="s">
         <v>235</v>
       </c>
-      <c r="M20" t="s">
-        <v>99</v>
-      </c>
-      <c r="N20" t="s">
-        <v>100</v>
-      </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
         <v>236</v>
       </c>
-      <c r="P20" t="s">
+      <c r="Q20" t="s">
+        <v>102</v>
+      </c>
+      <c r="R20" t="s">
         <v>237</v>
       </c>
-      <c r="Q20" t="s">
-        <v>103</v>
-      </c>
-      <c r="R20" t="s">
+      <c r="S20" t="s">
         <v>238</v>
       </c>
-      <c r="S20" t="s">
+      <c r="U20" t="s">
+        <v>99</v>
+      </c>
+      <c r="V20" t="s">
         <v>239</v>
-      </c>
-      <c r="T20" t="s">
-        <v>99</v>
-      </c>
-      <c r="U20" t="s">
-        <v>100</v>
-      </c>
-      <c r="V20" t="s">
-        <v>240</v>
       </c>
       <c r="W20" t="s">
         <v>15</v>
       </c>
       <c r="X20" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y20" t="s">
         <v>241</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>242</v>
       </c>
       <c r="Z20" t="s">
         <v>15</v>
       </c>
       <c r="AA20" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB20" t="s">
         <v>243</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>244</v>
       </c>
       <c r="AC20" t="s">
         <v>15</v>
       </c>
       <c r="AD20" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AE20" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AF20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B21" t="s">
+        <v>231</v>
+      </c>
+      <c r="C21" t="s">
+        <v>165</v>
+      </c>
+      <c r="D21" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" t="s">
         <v>166</v>
       </c>
-      <c r="C21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D21" t="s">
-        <v>167</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>232</v>
       </c>
-      <c r="F21" t="s">
+      <c r="H21" t="s">
+        <v>99</v>
+      </c>
+      <c r="I21" t="s">
         <v>233</v>
       </c>
-      <c r="G21" t="s">
-        <v>99</v>
-      </c>
-      <c r="H21" t="s">
-        <v>100</v>
-      </c>
-      <c r="I21" t="s">
+      <c r="K21" t="s">
+        <v>99</v>
+      </c>
+      <c r="L21" t="s">
         <v>234</v>
       </c>
-      <c r="J21" t="s">
-        <v>99</v>
-      </c>
-      <c r="K21" t="s">
-        <v>100</v>
-      </c>
-      <c r="L21" t="s">
+      <c r="N21" t="s">
+        <v>99</v>
+      </c>
+      <c r="O21" t="s">
         <v>235</v>
       </c>
-      <c r="M21" t="s">
-        <v>99</v>
-      </c>
-      <c r="N21" t="s">
-        <v>100</v>
-      </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>236</v>
       </c>
-      <c r="P21" t="s">
+      <c r="Q21" t="s">
+        <v>102</v>
+      </c>
+      <c r="R21" t="s">
         <v>237</v>
       </c>
-      <c r="Q21" t="s">
-        <v>103</v>
-      </c>
-      <c r="R21" t="s">
+      <c r="S21" t="s">
         <v>238</v>
       </c>
-      <c r="S21" t="s">
+      <c r="U21" t="s">
+        <v>99</v>
+      </c>
+      <c r="V21" t="s">
         <v>239</v>
-      </c>
-      <c r="T21" t="s">
-        <v>99</v>
-      </c>
-      <c r="U21" t="s">
-        <v>100</v>
-      </c>
-      <c r="V21" t="s">
-        <v>240</v>
       </c>
       <c r="W21" t="s">
         <v>15</v>
       </c>
       <c r="X21" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y21" t="s">
         <v>241</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>242</v>
       </c>
       <c r="Z21" t="s">
         <v>15</v>
       </c>
       <c r="AA21" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB21" t="s">
         <v>243</v>
-      </c>
-      <c r="AB21" t="s">
-        <v>244</v>
       </c>
       <c r="AC21" t="s">
         <v>15</v>
       </c>
       <c r="AD21" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AE21" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AF21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>

--- a/tests/ProcessCore.Tests/TestObjects/fct_gcqtof_assay.xlsx
+++ b/tests/ProcessCore.Tests/TestObjects/fct_gcqtof_assay.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F99EDA-FA90-42A1-BAD9-08813BA15E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2652BBC-1218-49F3-80A0-C959B1DB5160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25510" yWindow="0" windowWidth="25780" windowHeight="20970" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="isa_assay" sheetId="1" r:id="rId1"/>
@@ -853,7 +853,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -992,6 +992,10 @@
     <filterColumn colId="32" hiddenButton="1"/>
     <filterColumn colId="33" hiddenButton="1"/>
   </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AH21">
+    <sortCondition ref="F2:F21"/>
+    <sortCondition descending="1" ref="AB2:AB21"/>
+  </sortState>
   <tableColumns count="34">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Input [Sample Name]" totalsRowLabel="Total"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Protocol REF"/>
@@ -1406,14 +1410,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1421,7 +1425,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1429,7 +1433,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1437,7 +1441,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1445,17 +1449,17 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1463,7 +1467,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1471,7 +1475,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1479,7 +1483,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1487,7 +1491,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1495,12 +1499,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1520,7 +1524,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -1540,12 +1544,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -1556,7 +1560,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -1564,12 +1568,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -1580,7 +1584,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -1591,7 +1595,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>45</v>
       </c>
@@ -1602,7 +1606,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1613,7 +1617,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -1624,12 +1628,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>52</v>
       </c>
@@ -1649,9 +1653,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AL7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>55</v>
       </c>
@@ -1767,7 +1771,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>93</v>
       </c>
@@ -1865,7 +1869,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>118</v>
       </c>
@@ -1963,7 +1967,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>122</v>
       </c>
@@ -2061,7 +2065,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>126</v>
       </c>
@@ -2159,7 +2163,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>130</v>
       </c>
@@ -2257,7 +2261,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>133</v>
       </c>
@@ -2367,9 +2371,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AH21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>55</v>
       </c>
@@ -2473,7 +2477,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>163</v>
       </c>
@@ -2559,9 +2563,9 @@
         <v>176</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="B3" t="s">
         <v>164</v>
@@ -2630,13 +2634,10 @@
         <v>113</v>
       </c>
       <c r="AB3" t="s">
-        <v>177</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="AD3" t="s">
-        <v>179</v>
+        <v>99</v>
       </c>
       <c r="AE3" t="s">
         <v>175</v>
@@ -2645,12 +2646,12 @@
         <v>99</v>
       </c>
       <c r="AH3" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="B4" t="s">
         <v>164</v>
@@ -2731,12 +2732,12 @@
         <v>99</v>
       </c>
       <c r="AH4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="B5" t="s">
         <v>164</v>
@@ -2805,13 +2806,10 @@
         <v>113</v>
       </c>
       <c r="AB5" t="s">
-        <v>177</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="AD5" t="s">
-        <v>179</v>
+        <v>99</v>
       </c>
       <c r="AE5" t="s">
         <v>175</v>
@@ -2820,12 +2818,12 @@
         <v>99</v>
       </c>
       <c r="AH5" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>117</v>
+        <v>163</v>
       </c>
       <c r="B6" t="s">
         <v>164</v>
@@ -2840,13 +2838,13 @@
         <v>166</v>
       </c>
       <c r="F6" t="s">
-        <v>184</v>
+        <v>99</v>
       </c>
       <c r="G6" t="s">
-        <v>185</v>
+        <v>99</v>
       </c>
       <c r="H6" t="s">
-        <v>186</v>
+        <v>99</v>
       </c>
       <c r="I6" t="s">
         <v>167</v>
@@ -2894,10 +2892,13 @@
         <v>113</v>
       </c>
       <c r="AB6" t="s">
-        <v>174</v>
+        <v>177</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>178</v>
       </c>
       <c r="AD6" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="AE6" t="s">
         <v>175</v>
@@ -2906,12 +2907,12 @@
         <v>99</v>
       </c>
       <c r="AH6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>117</v>
+        <v>181</v>
       </c>
       <c r="B7" t="s">
         <v>164</v>
@@ -2926,13 +2927,13 @@
         <v>166</v>
       </c>
       <c r="F7" t="s">
-        <v>184</v>
+        <v>99</v>
       </c>
       <c r="G7" t="s">
-        <v>185</v>
+        <v>99</v>
       </c>
       <c r="H7" t="s">
-        <v>186</v>
+        <v>99</v>
       </c>
       <c r="I7" t="s">
         <v>167</v>
@@ -2995,12 +2996,12 @@
         <v>99</v>
       </c>
       <c r="AH7" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>121</v>
+        <v>163</v>
       </c>
       <c r="B8" t="s">
         <v>164</v>
@@ -3015,13 +3016,13 @@
         <v>166</v>
       </c>
       <c r="F8" t="s">
-        <v>184</v>
+        <v>99</v>
       </c>
       <c r="G8" t="s">
-        <v>185</v>
+        <v>99</v>
       </c>
       <c r="H8" t="s">
-        <v>186</v>
+        <v>99</v>
       </c>
       <c r="I8" t="s">
         <v>167</v>
@@ -3069,10 +3070,13 @@
         <v>113</v>
       </c>
       <c r="AB8" t="s">
-        <v>174</v>
+        <v>177</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>178</v>
       </c>
       <c r="AD8" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="AE8" t="s">
         <v>175</v>
@@ -3081,12 +3085,12 @@
         <v>99</v>
       </c>
       <c r="AH8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>121</v>
+        <v>201</v>
       </c>
       <c r="B9" t="s">
         <v>164</v>
@@ -3101,13 +3105,13 @@
         <v>166</v>
       </c>
       <c r="F9" t="s">
-        <v>184</v>
+        <v>99</v>
       </c>
       <c r="G9" t="s">
-        <v>185</v>
+        <v>99</v>
       </c>
       <c r="H9" t="s">
-        <v>186</v>
+        <v>99</v>
       </c>
       <c r="I9" t="s">
         <v>167</v>
@@ -3170,12 +3174,12 @@
         <v>99</v>
       </c>
       <c r="AH9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B10" t="s">
         <v>164</v>
@@ -3256,12 +3260,12 @@
         <v>99</v>
       </c>
       <c r="AH10" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B11" t="s">
         <v>164</v>
@@ -3330,13 +3334,10 @@
         <v>113</v>
       </c>
       <c r="AB11" t="s">
-        <v>177</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="AD11" t="s">
-        <v>179</v>
+        <v>99</v>
       </c>
       <c r="AE11" t="s">
         <v>175</v>
@@ -3345,12 +3346,12 @@
         <v>99</v>
       </c>
       <c r="AH11" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="B12" t="s">
         <v>164</v>
@@ -3365,13 +3366,13 @@
         <v>166</v>
       </c>
       <c r="F12" t="s">
-        <v>99</v>
+        <v>184</v>
       </c>
       <c r="G12" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="H12" t="s">
-        <v>99</v>
+        <v>186</v>
       </c>
       <c r="I12" t="s">
         <v>167</v>
@@ -3431,12 +3432,12 @@
         <v>99</v>
       </c>
       <c r="AH12" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="B13" t="s">
         <v>164</v>
@@ -3451,13 +3452,13 @@
         <v>166</v>
       </c>
       <c r="F13" t="s">
-        <v>99</v>
+        <v>184</v>
       </c>
       <c r="G13" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="H13" t="s">
-        <v>99</v>
+        <v>186</v>
       </c>
       <c r="I13" t="s">
         <v>167</v>
@@ -3505,13 +3506,10 @@
         <v>113</v>
       </c>
       <c r="AB13" t="s">
-        <v>177</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="AD13" t="s">
-        <v>179</v>
+        <v>99</v>
       </c>
       <c r="AE13" t="s">
         <v>175</v>
@@ -3520,12 +3518,12 @@
         <v>99</v>
       </c>
       <c r="AH13" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B14" t="s">
         <v>164</v>
@@ -3606,12 +3604,12 @@
         <v>99</v>
       </c>
       <c r="AH14" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B15" t="s">
         <v>164</v>
@@ -3680,13 +3678,10 @@
         <v>113</v>
       </c>
       <c r="AB15" t="s">
-        <v>177</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="AD15" t="s">
-        <v>179</v>
+        <v>99</v>
       </c>
       <c r="AE15" t="s">
         <v>175</v>
@@ -3695,12 +3690,12 @@
         <v>99</v>
       </c>
       <c r="AH15" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="B16" t="s">
         <v>164</v>
@@ -3769,10 +3764,13 @@
         <v>113</v>
       </c>
       <c r="AB16" t="s">
-        <v>174</v>
+        <v>177</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>178</v>
       </c>
       <c r="AD16" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="AE16" t="s">
         <v>175</v>
@@ -3781,12 +3779,12 @@
         <v>99</v>
       </c>
       <c r="AH16" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="17" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="B17" t="s">
         <v>164</v>
@@ -3870,12 +3868,12 @@
         <v>99</v>
       </c>
       <c r="AH17" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="18" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B18" t="s">
         <v>164</v>
@@ -3944,10 +3942,13 @@
         <v>113</v>
       </c>
       <c r="AB18" t="s">
-        <v>174</v>
+        <v>177</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>178</v>
       </c>
       <c r="AD18" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="AE18" t="s">
         <v>175</v>
@@ -3956,12 +3957,12 @@
         <v>99</v>
       </c>
       <c r="AH18" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="19" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B19" t="s">
         <v>164</v>
@@ -4045,12 +4046,12 @@
         <v>99</v>
       </c>
       <c r="AH19" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>201</v>
+        <v>132</v>
       </c>
       <c r="B20" t="s">
         <v>164</v>
@@ -4065,13 +4066,13 @@
         <v>166</v>
       </c>
       <c r="F20" t="s">
-        <v>99</v>
+        <v>184</v>
       </c>
       <c r="G20" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="H20" t="s">
-        <v>99</v>
+        <v>186</v>
       </c>
       <c r="I20" t="s">
         <v>167</v>
@@ -4119,10 +4120,13 @@
         <v>113</v>
       </c>
       <c r="AB20" t="s">
-        <v>174</v>
+        <v>177</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>178</v>
       </c>
       <c r="AD20" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="AE20" t="s">
         <v>175</v>
@@ -4131,12 +4135,12 @@
         <v>99</v>
       </c>
       <c r="AH20" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="21" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>201</v>
+        <v>135</v>
       </c>
       <c r="B21" t="s">
         <v>164</v>
@@ -4151,13 +4155,13 @@
         <v>166</v>
       </c>
       <c r="F21" t="s">
-        <v>99</v>
+        <v>184</v>
       </c>
       <c r="G21" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="H21" t="s">
-        <v>99</v>
+        <v>186</v>
       </c>
       <c r="I21" t="s">
         <v>167</v>
@@ -4220,7 +4224,7 @@
         <v>99</v>
       </c>
       <c r="AH21" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -4235,9 +4239,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AG21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>55</v>
       </c>
@@ -4338,7 +4342,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>176</v>
       </c>
@@ -4427,7 +4431,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>180</v>
       </c>
@@ -4516,7 +4520,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>182</v>
       </c>
@@ -4605,7 +4609,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>183</v>
       </c>
@@ -4694,7 +4698,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>187</v>
       </c>
@@ -4783,7 +4787,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>188</v>
       </c>
@@ -4872,7 +4876,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>189</v>
       </c>
@@ -4961,7 +4965,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>190</v>
       </c>
@@ -5050,7 +5054,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>191</v>
       </c>
@@ -5139,7 +5143,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>192</v>
       </c>
@@ -5228,7 +5232,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>193</v>
       </c>
@@ -5317,7 +5321,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>194</v>
       </c>
@@ -5406,7 +5410,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>195</v>
       </c>
@@ -5495,7 +5499,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>196</v>
       </c>
@@ -5584,7 +5588,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>197</v>
       </c>
@@ -5673,7 +5677,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>198</v>
       </c>
@@ -5762,7 +5766,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>199</v>
       </c>
@@ -5851,7 +5855,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>200</v>
       </c>
@@ -5940,7 +5944,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>202</v>
       </c>
@@ -6029,7 +6033,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>203</v>
       </c>
